--- a/2022 data/excel_outputs/383_boothwise_data.xlsx
+++ b/2022 data/excel_outputs/383_boothwise_data.xlsx
@@ -14,750 +14,1449 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="502">
   <si>
     <t>AC 383 Booth-wise Data</t>
   </si>
   <si>
+    <t>Unnamed: 1</t>
+  </si>
+  <si>
+    <t>Unnamed: 2</t>
+  </si>
+  <si>
+    <t>Unnamed: 3</t>
+  </si>
+  <si>
+    <t>Unnamed: 4</t>
+  </si>
+  <si>
+    <t>Unnamed: 5</t>
+  </si>
+  <si>
+    <t>Unnamed: 6</t>
+  </si>
+  <si>
+    <t>Unnamed: 7</t>
+  </si>
+  <si>
+    <t>Unnamed: 8</t>
+  </si>
+  <si>
+    <t>Unnamed: 9</t>
+  </si>
+  <si>
+    <t>Unnamed: 10</t>
+  </si>
+  <si>
+    <t>Unnamed: 11</t>
+  </si>
+  <si>
+    <t>Unnamed: 12</t>
+  </si>
+  <si>
+    <t>Unnamed: 13</t>
+  </si>
+  <si>
+    <t>Unnamed: 14</t>
+  </si>
+  <si>
+    <t>Unnamed: 15</t>
+  </si>
+  <si>
+    <t>Unnamed: 16</t>
+  </si>
+  <si>
+    <t>Unnamed: 17</t>
+  </si>
+  <si>
+    <t>Unnamed: 18</t>
+  </si>
+  <si>
+    <t>Unnamed: 19</t>
+  </si>
+  <si>
+    <t>Unnamed: 20</t>
+  </si>
+  <si>
+    <t>Unnamed: 21</t>
+  </si>
+  <si>
+    <t>Unnamed: 22</t>
+  </si>
+  <si>
     <t>BOOTH ID</t>
   </si>
   <si>
     <t>POLLING STATION NAME</t>
   </si>
   <si>
-    <t>####0##0 ######</t>
-  </si>
-  <si>
-    <t>######## ##0 ##### ### #### ###.1</t>
-  </si>
-  <si>
-    <t>######## ##0 ##### ### #### ###.2</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #### ###.1</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #### ###.2</t>
-  </si>
-  <si>
-    <t>######## ##0 ######### #####</t>
-  </si>
-  <si>
-    <t>#######0 #######</t>
-  </si>
-  <si>
-    <t>#######0 ########</t>
-  </si>
-  <si>
-    <t>#######0 ######## #### ### .1</t>
-  </si>
-  <si>
-    <t>#######0 ######## #### ### .2</t>
-  </si>
-  <si>
-    <t>##0##0###################</t>
-  </si>
-  <si>
-    <t>######## ##0 ######## #### ### .1</t>
-  </si>
-  <si>
-    <t>######## ##0 ######## #### ### .2</t>
-  </si>
-  <si>
-    <t>######## ##0 ##########</t>
-  </si>
-  <si>
-    <t>#######0 #### #### ###.1</t>
-  </si>
-  <si>
-    <t>#######0 #### #### ###.2</t>
-  </si>
-  <si>
-    <t>######## ##0 ###### #### ### .1</t>
-  </si>
-  <si>
-    <t>######## ##0 ###### #### ### .2</t>
-  </si>
-  <si>
-    <t>######## ##0 ###### #### ### .3</t>
-  </si>
-  <si>
-    <t>#######0 ##### #### ### .1</t>
-  </si>
-  <si>
-    <t>#######0 ##### #### ### .2</t>
-  </si>
-  <si>
-    <t>######## ##0 ##### #### ### 1</t>
-  </si>
-  <si>
-    <t>######## ##0 ##### #### ### 3</t>
-  </si>
-  <si>
-    <t>######## ##0 ##### #### ### 2</t>
-  </si>
-  <si>
-    <t>######## ##0 ##### #### ### 4</t>
-  </si>
-  <si>
-    <t>######## ##0 ####### #### ### .1</t>
-  </si>
-  <si>
-    <t>######## ##0 ####### #### ### .2</t>
-  </si>
-  <si>
-    <t>######## ##0 ####### #### ### .3</t>
-  </si>
-  <si>
-    <t>#######0 ########## #### ### .1</t>
-  </si>
-  <si>
-    <t>#######0 ########## #### ### .2</t>
-  </si>
-  <si>
-    <t>#######0 ######### #### ### 1</t>
-  </si>
-  <si>
-    <t>#######0 ######### #### ### 2</t>
-  </si>
-  <si>
-    <t>##0##0##### ######## ### #### ###.1</t>
-  </si>
-  <si>
-    <t>##0##0#####0######## ### #### ###.2</t>
-  </si>
-  <si>
-    <t>######## ##0 #######</t>
-  </si>
-  <si>
-    <t>#######0 ##### ### 1</t>
-  </si>
-  <si>
-    <t>#######0 ##### ### 2</t>
-  </si>
-  <si>
-    <t>#######0 ###### #### ### 1</t>
-  </si>
-  <si>
-    <t>#######0 ###### #### ### .2</t>
-  </si>
-  <si>
-    <t>##0##0##### ##### #### ### 1</t>
-  </si>
-  <si>
-    <t>##0##0##### ##### #### ### 2</t>
-  </si>
-  <si>
-    <t>#######0 #### ###</t>
-  </si>
-  <si>
-    <t>#######0 #####</t>
-  </si>
-  <si>
-    <t>######## ##0 ###### ##### #### ### 1</t>
-  </si>
-  <si>
-    <t>######## ##0 ###### ##### #### ### 2</t>
-  </si>
-  <si>
-    <t>#######0 ####### #### ### 1</t>
-  </si>
-  <si>
-    <t>#######0 ####### #### ### 2</t>
-  </si>
-  <si>
-    <t>######## ##0 ######</t>
-  </si>
-  <si>
-    <t>######## ##0 ####</t>
-  </si>
-  <si>
-    <t>######## ##0 ####### #### ###.1</t>
-  </si>
-  <si>
-    <t>#######0 ##</t>
-  </si>
-  <si>
-    <t>######## ##0 ##### #### ###.1</t>
-  </si>
-  <si>
-    <t>######## ##0 ##### #### ###.4</t>
-  </si>
-  <si>
-    <t>######## ##0 ##### #### ###.2</t>
-  </si>
-  <si>
-    <t>######## ##0 ##### #### ###.3</t>
-  </si>
-  <si>
-    <t>######## ##0 ##### #### ###.5</t>
-  </si>
-  <si>
-    <t>####0##0 ########</t>
-  </si>
-  <si>
-    <t>######## ##0 ######### #### ###.1</t>
-  </si>
-  <si>
-    <t>######## ##0 ######### #### ###.2</t>
-  </si>
-  <si>
-    <t>#######0 ##### ##### #### ###.1</t>
-  </si>
-  <si>
-    <t>#######0 ##### ##### #### ###.2</t>
-  </si>
-  <si>
-    <t>####0##0 ####### #### ###.1</t>
-  </si>
-  <si>
-    <t>####0##0 ####### #### ###.2</t>
-  </si>
-  <si>
-    <t>#######0 ######## #####</t>
-  </si>
-  <si>
-    <t>#######0 ######### ###</t>
-  </si>
-  <si>
-    <t>######## ##0 ##### ###### #### ##0.1</t>
-  </si>
-  <si>
-    <t>######## ##0 ##### ###### #### ##0.2</t>
-  </si>
-  <si>
-    <t>#######0#### #### ### .2</t>
-  </si>
-  <si>
-    <t>#######0 ####### #### ###.1</t>
-  </si>
-  <si>
-    <t>######## ####### #### ###.2</t>
-  </si>
-  <si>
-    <t>######## #####</t>
-  </si>
-  <si>
-    <t>####0##0 ###########</t>
-  </si>
-  <si>
-    <t>######## ##0 ########</t>
-  </si>
-  <si>
-    <t>######## ##0 ##### #### ### .1</t>
-  </si>
-  <si>
-    <t>######## ##0 ##### #### ### .2</t>
-  </si>
-  <si>
-    <t>######## ########## ######</t>
-  </si>
-  <si>
-    <t>######## ####</t>
-  </si>
-  <si>
-    <t>######## ###### #### ###.1</t>
-  </si>
-  <si>
-    <t>######## ###### #### ###.2</t>
-  </si>
-  <si>
-    <t>################## #### ###.1</t>
-  </si>
-  <si>
-    <t>################## #### ###.2</t>
-  </si>
-  <si>
-    <t>######## ##0 #####</t>
-  </si>
-  <si>
-    <t>###### #### ##### #######</t>
-  </si>
-  <si>
-    <t>######## ##0 ####### #### ###.2</t>
-  </si>
-  <si>
-    <t>##0##0##0 ##### #### ###.1</t>
-  </si>
-  <si>
-    <t>##0##0##0 ##### #### ###.2</t>
-  </si>
-  <si>
-    <t>##0##0##0##0##### ##### ######</t>
-  </si>
-  <si>
-    <t>################# #### ###.1</t>
-  </si>
-  <si>
-    <t>################# #### ###.2</t>
-  </si>
-  <si>
-    <t>####################</t>
-  </si>
-  <si>
-    <t>##0##0##0 ############ #### ###.1</t>
-  </si>
-  <si>
-    <t>##0##0##0 ############ #### ###.2</t>
-  </si>
-  <si>
-    <t>######## ######</t>
-  </si>
-  <si>
-    <t>######## ###</t>
-  </si>
-  <si>
-    <t>######## ##### #### ###.1</t>
-  </si>
-  <si>
-    <t>######## ##### #### ###.2</t>
-  </si>
-  <si>
-    <t>######## ##0 #### #### ###.1</t>
-  </si>
-  <si>
-    <t>######## ##0 #### #### ###.2</t>
-  </si>
-  <si>
-    <t>######## ####### #### ###.1</t>
-  </si>
-  <si>
-    <t>###############</t>
-  </si>
-  <si>
-    <t>######## #######</t>
-  </si>
-  <si>
-    <t>######## ##0 ##### ###</t>
-  </si>
-  <si>
-    <t>##0##0##### #####</t>
-  </si>
-  <si>
-    <t>###### ### ###########</t>
-  </si>
-  <si>
-    <t>###### ### ####</t>
-  </si>
-  <si>
-    <t>######## #### #### ###.1</t>
-  </si>
-  <si>
-    <t>######## #### #### ###.2</t>
-  </si>
-  <si>
-    <t>######## ######## ####</t>
-  </si>
-  <si>
-    <t>######## ##### #####</t>
-  </si>
-  <si>
-    <t>######## ##### #######</t>
-  </si>
-  <si>
-    <t>#### ###### ###### ##### #### ###.1</t>
-  </si>
-  <si>
-    <t>#### ###### ###### ##### #### ###.2</t>
-  </si>
-  <si>
-    <t>######## ##### ###</t>
-  </si>
-  <si>
-    <t>### ##### ##### ##### #####</t>
-  </si>
-  <si>
-    <t>######## ### #### ###.1</t>
-  </si>
-  <si>
-    <t>######## ### #### ###.2</t>
-  </si>
-  <si>
-    <t>######## ######## #### ###.1</t>
-  </si>
-  <si>
-    <t>######## ######## #### ###.2</t>
-  </si>
-  <si>
-    <t>######## #########</t>
-  </si>
-  <si>
-    <t>######## ########</t>
-  </si>
-  <si>
-    <t>######## ###########</t>
-  </si>
-  <si>
-    <t>######## ###### ###### #### ###.1</t>
-  </si>
-  <si>
-    <t>######## ###### ###### #### ###.2</t>
-  </si>
-  <si>
-    <t>######## ###### ###</t>
-  </si>
-  <si>
-    <t>######## ###### ######</t>
-  </si>
-  <si>
-    <t>######## #### ######</t>
-  </si>
-  <si>
-    <t>######## ##0 ####### #### ###.3</t>
-  </si>
-  <si>
-    <t>##0##0##0 ####### #### ###.1</t>
-  </si>
-  <si>
-    <t>##0##0##0 ####### #### ###.2</t>
-  </si>
-  <si>
-    <t>######## ##0 ####### #### ###.4</t>
-  </si>
-  <si>
-    <t>####0##0 ########## #### ###.1</t>
-  </si>
-  <si>
-    <t>####0##0 ########## #### ###.2</t>
-  </si>
-  <si>
-    <t>####0### #####</t>
-  </si>
-  <si>
-    <t>######## ##0 ###### #### ###.1</t>
-  </si>
-  <si>
-    <t>######## ##0 ###### #### ###.2</t>
-  </si>
-  <si>
-    <t>###### ### #####</t>
-  </si>
-  <si>
-    <t>####0### ########</t>
-  </si>
-  <si>
-    <t>####0### #######</t>
-  </si>
-  <si>
-    <t>####0##0 #######</t>
-  </si>
-  <si>
-    <t>##### #0####0##0 ###########</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #####</t>
-  </si>
-  <si>
-    <t>####0##0 #### #######</t>
-  </si>
-  <si>
-    <t>####0##0 ########### ;#######ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ######## #### ###.1</t>
-  </si>
-  <si>
-    <t>####0##0 ######## #### ###.2</t>
-  </si>
-  <si>
-    <t>####0##0 ####</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ###</t>
-  </si>
-  <si>
-    <t>####0##0 ##########</t>
-  </si>
-  <si>
-    <t>####0##0 #### ###### #### ###.1</t>
-  </si>
-  <si>
-    <t>####0##0 #### ###### #### ###.2</t>
-  </si>
-  <si>
-    <t>####0##0 #########</t>
-  </si>
-  <si>
-    <t>####0##0 ########## ####### #### ###.1</t>
-  </si>
-  <si>
-    <t>####0##0 ########## ####### #### ###.2</t>
-  </si>
-  <si>
-    <t>#0####0##0 ########## #### ### .1</t>
-  </si>
-  <si>
-    <t>#0####0##0 ########## #### ### .3</t>
-  </si>
-  <si>
-    <t>#0####0##0 ########## #### ### .2</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ###### #### ###.1</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ###### #### ###.2</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ###### #### ###.3</t>
-  </si>
-  <si>
-    <t>######## ##0 ####### #### ##0.3</t>
-  </si>
-  <si>
-    <t>######## ##0 ####### #### ##0.1</t>
-  </si>
-  <si>
-    <t>######## ##0 ####### #### ##0.2</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #0</t>
-  </si>
-  <si>
-    <t>######## ##0 #########</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #### ##0.1</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #### ##0.2</t>
-  </si>
-  <si>
-    <t>#0##0##0 ##### ##### ##### #### ###.1</t>
-  </si>
-  <si>
-    <t>#0##0##0 ##### ##### ##### #### ###.2</t>
-  </si>
-  <si>
-    <t>#0####0##0 ##### #### ###.1</t>
-  </si>
-  <si>
-    <t>#0####0##0 ##### #### ###.2</t>
-  </si>
-  <si>
-    <t>####0##0 #### ####</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ####### #### ###.1</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ####### #### ###.2</t>
-  </si>
-  <si>
-    <t>######## ### #### ##### #### ###.1</t>
-  </si>
-  <si>
-    <t>######## ### #### ##### #### ###.3</t>
-  </si>
-  <si>
-    <t>######## ### #### ##### #### ###.2</t>
-  </si>
-  <si>
-    <t>##### #0##0##0##### #### ###.1</t>
-  </si>
-  <si>
-    <t>##### #0##0##0##### #### ###.2</t>
-  </si>
-  <si>
-    <t>#### ###### ##### ##### #### ###.1</t>
-  </si>
-  <si>
-    <t>#### ###### ##### ##### #### ###.2</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ##### #### ###.1</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ##### #### ###.2</t>
-  </si>
-  <si>
-    <t>####0##0 ########### #### ###.1</t>
-  </si>
-  <si>
-    <t>####0##0 ########### #### ###.2</t>
-  </si>
-  <si>
-    <t>####0##0 #####</t>
-  </si>
-  <si>
-    <t>##### ##### ##### ####### #### ###.1</t>
-  </si>
-  <si>
-    <t>##### ##### ##### ####### #### ###.3</t>
-  </si>
-  <si>
-    <t>##### ##### ##### ####### #### ###.2</t>
-  </si>
-  <si>
-    <t>##### ##### ##### ####### #### ###.4</t>
-  </si>
-  <si>
-    <t>####0##0 ##### #### ###.1</t>
-  </si>
-  <si>
-    <t>####0##0 ##### #### ###.2</t>
-  </si>
-  <si>
-    <t>###### ### ######</t>
-  </si>
-  <si>
-    <t>####0##0 #### ##### #### ###.1</t>
-  </si>
-  <si>
-    <t>####0##0 #### ##### #### ###.2</t>
-  </si>
-  <si>
-    <t>##### ### #### ####### #### ###.1</t>
-  </si>
-  <si>
-    <t>##### ### #### ####### #### ###.2</t>
-  </si>
-  <si>
-    <t>##### ### ######### ###</t>
-  </si>
-  <si>
-    <t>##### ### ##### ##### #### ###.1</t>
-  </si>
-  <si>
-    <t>##### ### ##### ##### #### ###.2</t>
-  </si>
-  <si>
-    <t>#0####0##0 ##### ### #### ###.1</t>
-  </si>
-  <si>
-    <t>#0####0##0 ##### ### #### ###.2</t>
-  </si>
-  <si>
-    <t>######## ##0 ###### ###</t>
-  </si>
-  <si>
-    <t>##### ##0 ######</t>
-  </si>
-  <si>
-    <t>##### ##0 ########</t>
-  </si>
-  <si>
-    <t>######## ##0 #### #######</t>
-  </si>
-  <si>
-    <t>##### ### ########</t>
-  </si>
-  <si>
-    <t>##############0 ######## #### ###.1</t>
-  </si>
-  <si>
-    <t>####################### #### ###.2</t>
-  </si>
-  <si>
-    <t>######## ##0 ###### ####### #### ###.1</t>
-  </si>
-  <si>
-    <t>######## ##0 ###### ####### #### ###.2</t>
-  </si>
-  <si>
-    <t>######## ##0############## #### ###.1</t>
-  </si>
-  <si>
-    <t>######## ##0############## #### ###.2</t>
-  </si>
-  <si>
-    <t>######## ########### #### ###.1</t>
-  </si>
-  <si>
-    <t>######## ########### #### ###.2</t>
-  </si>
-  <si>
-    <t>######## ##########</t>
-  </si>
-  <si>
-    <t>######## ##0 ########## #### ###.1</t>
-  </si>
-  <si>
-    <t>######## ##0 ########## #### ###.3</t>
-  </si>
-  <si>
-    <t>######## ##0 ########## #### ###.2</t>
-  </si>
-  <si>
-    <t>##### ##0 ##0 ####</t>
-  </si>
-  <si>
-    <t>#######0 ######## ####</t>
-  </si>
-  <si>
-    <t>#######0 ######## #######</t>
-  </si>
-  <si>
-    <t>#######0 ######### #### ###.1</t>
-  </si>
-  <si>
-    <t>#######0 ######### #### ###.2</t>
-  </si>
-  <si>
-    <t>#######0 ######</t>
-  </si>
-  <si>
-    <t>########### ### ##### ######</t>
-  </si>
-  <si>
-    <t>#######0 ###### #####</t>
-  </si>
-  <si>
-    <t>######## ##0 #############</t>
-  </si>
-  <si>
-    <t>##0##0##### ##### ###</t>
-  </si>
-  <si>
-    <t>######## #### #### ###.3</t>
-  </si>
-  <si>
-    <t>##0##0##0 ######</t>
-  </si>
-  <si>
-    <t>######## ##0 ######## #### ###.1</t>
-  </si>
-  <si>
-    <t>######## ##0 ######## #### ###.2</t>
-  </si>
-  <si>
-    <t>#######0 #############</t>
-  </si>
-  <si>
-    <t>######## ##0 ### #### ###.1</t>
-  </si>
-  <si>
-    <t>######## ##0 ### #### ###.2</t>
-  </si>
-  <si>
-    <t>######## ####### ## ##### #######</t>
-  </si>
-  <si>
-    <t>##0##0##0##0##### ####### #### ###.1</t>
-  </si>
-  <si>
-    <t>##0##0##0##0##### ####### #### ###.2</t>
-  </si>
-  <si>
-    <t>##0##0#0#####</t>
-  </si>
-  <si>
-    <t>#######0 ####</t>
-  </si>
-  <si>
-    <t>######## ##0 ######## ###</t>
-  </si>
-  <si>
-    <t>#######0 #########</t>
-  </si>
-  <si>
-    <t>#######0 ##########</t>
-  </si>
-  <si>
-    <t>#######0###### #### ###.1</t>
-  </si>
-  <si>
-    <t>#######0###### #### ###.2</t>
+    <t>P.P.CHHITTO</t>
+  </si>
+  <si>
+    <t>P.P.MAJHWAR KHAS KAKSH N.-1</t>
+  </si>
+  <si>
+    <t>P.P.MAJHWAR KHAS ROOM N.-2</t>
+  </si>
+  <si>
+    <t>P.P.FUTIYA</t>
+  </si>
+  <si>
+    <t>P.P.NARASINGHPUR KHURD</t>
+  </si>
+  <si>
+    <t>P.P.MADHOPUR</t>
+  </si>
+  <si>
+    <t>P.P.LILAPUR</t>
+  </si>
+  <si>
+    <t>P.P.JAYRAMPUR</t>
+  </si>
+  <si>
+    <t>P.P.BHAGWANPUR</t>
+  </si>
+  <si>
+    <t>J.H.SCHOOLSAWAIYAPATTADARI</t>
+  </si>
+  <si>
+    <t>P.P.MACHIYAKALA ROOM N.-1</t>
+  </si>
+  <si>
+    <t>MACHIYAKALA ROOM N. -2</t>
+  </si>
+  <si>
+    <t>P.P.DARVESHPUR</t>
+  </si>
+  <si>
+    <t>P.P.DAUDPUR</t>
+  </si>
+  <si>
+    <t>P.P.SULTANPUR</t>
+  </si>
+  <si>
+    <t>P.P.WAJIDPUR</t>
+  </si>
+  <si>
+    <t>P.P.NAWAHI ROOM N.-1</t>
+  </si>
+  <si>
+    <t>P.P.NAWAHI ROOM N.-2</t>
+  </si>
+  <si>
+    <t>P.P.NEGURA ROOM N.-1</t>
+  </si>
+  <si>
+    <t>P.P.NEGURA ROOM N.-2</t>
+  </si>
+  <si>
+    <t>P.P.MASAUNI</t>
+  </si>
+  <si>
+    <t>P.P.PAITUA ROOM N.1</t>
+  </si>
+  <si>
+    <t>P.P.PAITUA ROOM N.-2</t>
+  </si>
+  <si>
+    <t>P.P.HATHIYANI ROOM N.-1</t>
+  </si>
+  <si>
+    <t>P.P.HATHIYANI ROOM N.-2</t>
+  </si>
+  <si>
+    <t>P.P.MUSTFAPUR ROOM N.-1</t>
+  </si>
+  <si>
+    <t>P.P.MUSTFAPUR ROOM N.-2</t>
+  </si>
+  <si>
+    <t>P.P.PRATAPPUR ROOM N.-1</t>
+  </si>
+  <si>
+    <t>P.P.PRATAPPUR ROOM N.-2</t>
+  </si>
+  <si>
+    <t>J.H.SCHOOL FATTEPUR KALA ROOM N.-1</t>
+  </si>
+  <si>
+    <t>J.H.SCHOOLFATTEPUR KALA ROOM N.-2</t>
+  </si>
+  <si>
+    <t>P.P.NARAYANPUR</t>
+  </si>
+  <si>
+    <t>P.P.VIJAYPUR</t>
+  </si>
+  <si>
+    <t>P.P.MAGARAHI</t>
+  </si>
+  <si>
+    <t>P.P.AURAIYA</t>
+  </si>
+  <si>
+    <t>P.P.SUDANV ROOM N. -1</t>
+  </si>
+  <si>
+    <t>P.P.SUDANV ROOM N. -2</t>
+  </si>
+  <si>
+    <t>P.P.ALAHLADPUR</t>
+  </si>
+  <si>
+    <t>J.H.SCHOOLMAIDHI</t>
+  </si>
+  <si>
+    <t>P.P.NARAHAN KALA</t>
+  </si>
+  <si>
+    <t>P.P.BHAWARAHI</t>
+  </si>
+  <si>
+    <t>P.P.TIRRO</t>
+  </si>
+  <si>
+    <t>P.P.GHANAPUR</t>
+  </si>
+  <si>
+    <t>P.P.KONIYA</t>
+  </si>
+  <si>
+    <t>P.P.DHARAULI ROOM N.-1</t>
+  </si>
+  <si>
+    <t>P.P.DHARAULI ROOM N.-2</t>
+  </si>
+  <si>
+    <t>P.P. AILAHI</t>
+  </si>
+  <si>
+    <t>P.P.SOHADWAR ROOM N.-1</t>
+  </si>
+  <si>
+    <t>P.P.SOHADWAR ROOM N.-2</t>
+  </si>
+  <si>
+    <t>P.P.CHAK</t>
+  </si>
+  <si>
+    <t>P.P.URAGANW</t>
+  </si>
+  <si>
+    <t>P.P.JALALPUR</t>
+  </si>
+  <si>
+    <t>P.P.KANTA ROOM N. -1</t>
+  </si>
+  <si>
+    <t>P.P.KANTA ROOM N. -2</t>
+  </si>
+  <si>
+    <t>P.P.KANTA ROOM N. -3</t>
+  </si>
+  <si>
+    <t>P.P.JAGDISHPUR</t>
+  </si>
+  <si>
+    <t>P.P.VISHUNPURA ROOM N.-1</t>
+  </si>
+  <si>
+    <t>P.P.VISHUNPURA ROOM N.-2</t>
+  </si>
+  <si>
+    <t>P.P.BHADAULIYA</t>
+  </si>
+  <si>
+    <t>P.P.JAMOKHAR</t>
+  </si>
+  <si>
+    <t>P.P.PARASI KHURD</t>
+  </si>
+  <si>
+    <t>P.P.PAKHANPURA</t>
+  </si>
+  <si>
+    <t>P.P.RAJJUPUR</t>
+  </si>
+  <si>
+    <t>P.P.FATTEPUR KHURD</t>
+  </si>
+  <si>
+    <t>P.P.PARASI KALA ROOM N.-1</t>
+  </si>
+  <si>
+    <t>P.P.PARASI KALA ROOM N.-2</t>
+  </si>
+  <si>
+    <t>P.P.MANIKPUR</t>
+  </si>
+  <si>
+    <t>P.P.SAWAIYA MAHALWAR</t>
+  </si>
+  <si>
+    <t>P.P.HALUA ROOM N.-1</t>
+  </si>
+  <si>
+    <t>P.P.HALUA ROOM N.-2</t>
+  </si>
+  <si>
+    <t>P.P.JENGURI</t>
+  </si>
+  <si>
+    <t>P.P. PACHAPARA</t>
+  </si>
+  <si>
+    <t>P.P.KERAYGANW</t>
+  </si>
+  <si>
+    <t>P.P.PAHADPUR</t>
+  </si>
+  <si>
+    <t>P.P.GOVINDIPUR</t>
+  </si>
+  <si>
+    <t>P.P.RAMMADO</t>
+  </si>
+  <si>
+    <t>P.P.SINGHRAUL</t>
+  </si>
+  <si>
+    <t>P.P.BHATARAUL ROOM N.-1</t>
+  </si>
+  <si>
+    <t>P.P.BHATARAUL ROOM N.-2</t>
+  </si>
+  <si>
+    <t>P.P.BASANIYA</t>
+  </si>
+  <si>
+    <t>P.P.SOTA</t>
+  </si>
+  <si>
+    <t>P.P.INDRAPURAWA</t>
+  </si>
+  <si>
+    <t>P.P.KHARID</t>
+  </si>
+  <si>
+    <t>P.P.BHAWPUR</t>
+  </si>
+  <si>
+    <t>P.P.JAMUWA</t>
+  </si>
+  <si>
+    <t>P.P.BHAISAHI</t>
+  </si>
+  <si>
+    <t>J.H. SCHOOL BHARUHIYA</t>
+  </si>
+  <si>
+    <t>P.P.UDAYPURA ROOM N.-1</t>
+  </si>
+  <si>
+    <t>P.P.UDAYPURA ROOM N.-2</t>
+  </si>
+  <si>
+    <t>P.P.GAJDHARA</t>
+  </si>
+  <si>
+    <t>P.P.LATAV</t>
+  </si>
+  <si>
+    <t>P.P.BHODASAR ROOM N.-1</t>
+  </si>
+  <si>
+    <t>P.P.BHODASAR ROOM N.-2</t>
+  </si>
+  <si>
+    <t>P.P.IMILIYA</t>
+  </si>
+  <si>
+    <t>J.H.SCHOOL KHAKHADA ROOM N.-1</t>
+  </si>
+  <si>
+    <t>J.S.SCHOOL KHAKHADA ROOM N.-2</t>
+  </si>
+  <si>
+    <t>P.P.ROHAKHI</t>
+  </si>
+  <si>
+    <t>SU.SA.SEMA.VI.KHILACHI RAJADIHA ROOM N.-1</t>
+  </si>
+  <si>
+    <t>SU.SA.SEMA.VI.KHILACHI RAJADIHA ROOM N.-2</t>
+  </si>
+  <si>
+    <t>P.P.BARIYARPUR</t>
+  </si>
+  <si>
+    <t>P.P.GHODASARI</t>
+  </si>
+  <si>
+    <t>P.P.MASOI</t>
+  </si>
+  <si>
+    <t>P.P.BHUSIKRITPURAWA ROOM N.-1</t>
+  </si>
+  <si>
+    <t>P.P.BHUSIKRITPURAWA ROOM N. -2</t>
+  </si>
+  <si>
+    <t>P.P.NAUDIHA</t>
+  </si>
+  <si>
+    <t>P.P.TIYARA ROOM N.-1</t>
+  </si>
+  <si>
+    <t>P.P.TIYARA ROOM N.-2</t>
+  </si>
+  <si>
+    <t>P.P.KUA</t>
+  </si>
+  <si>
+    <t>P.P.NASARATHA</t>
+  </si>
+  <si>
+    <t>P.P.DADARA</t>
+  </si>
+  <si>
+    <t>P.P.DHARADE ROOM N.-1</t>
+  </si>
+  <si>
+    <t>P.P.DHARADE ROOM N.-2</t>
+  </si>
+  <si>
+    <t>J.H.SCHOOL MAWAIYA</t>
+  </si>
+  <si>
+    <t>P.P.CHITAUDI ROOM N.-1</t>
+  </si>
+  <si>
+    <t>P.P.CHITAUDI ROOM N.-2</t>
+  </si>
+  <si>
+    <t>P.P.KODOCHAK</t>
+  </si>
+  <si>
+    <t>P.P.AKODHAWA MU. KODOCHAK</t>
+  </si>
+  <si>
+    <t>P.P.DABARIKALA</t>
+  </si>
+  <si>
+    <t>P.P.VITHAWAL KALA</t>
+  </si>
+  <si>
+    <t>P.P.UTRAUT</t>
+  </si>
+  <si>
+    <t>KISAN SAHKARI SAMITI UTRAUT</t>
+  </si>
+  <si>
+    <t>P.P.GAURI</t>
+  </si>
+  <si>
+    <t>P.P.CHANDIPUR</t>
+  </si>
+  <si>
+    <t>P.P.HARIPUR</t>
+  </si>
+  <si>
+    <t>PANCHAYAT BHAWANSADIMURAKAWAL</t>
+  </si>
+  <si>
+    <t>PANCHAYAT BHAWAN AMANV</t>
+  </si>
+  <si>
+    <t>P.P. AMANV ROOM N,-1</t>
+  </si>
+  <si>
+    <t>P.P. AMANV ROOM N,-2</t>
+  </si>
+  <si>
+    <t>P.P. HADAURA</t>
+  </si>
+  <si>
+    <t>P.P.KAWALPURAWA MAFI</t>
+  </si>
+  <si>
+    <t>P.P.BHUDAKUDA</t>
+  </si>
+  <si>
+    <t>P.P.ILIYA</t>
+  </si>
+  <si>
+    <t>MANGAL VIDYA MANDIR ILIYA ROOM N.-1</t>
+  </si>
+  <si>
+    <t>MANGAL VIDYA MANDIR ILIYA ROOM N.-2</t>
+  </si>
+  <si>
+    <t>P.P.NICHOT KALA</t>
+  </si>
+  <si>
+    <t>RAM KRISHN INTER COLLAGE TIYARI</t>
+  </si>
+  <si>
+    <t>P.P. TIYARI</t>
+  </si>
+  <si>
+    <t>P.P. BEN ROOM N.-1</t>
+  </si>
+  <si>
+    <t>P.P. BEN ROOM N.-2</t>
+  </si>
+  <si>
+    <t>P.P.JIGANA</t>
+  </si>
+  <si>
+    <t>P.P. AMARASIPUR</t>
+  </si>
+  <si>
+    <t>P.P. AKAUNA</t>
+  </si>
+  <si>
+    <t>P.P.SARINGPUR</t>
+  </si>
+  <si>
+    <t>P.P.BADAGANVA ROOM N.-1</t>
+  </si>
+  <si>
+    <t>P.P. BADAGANVA ROOM N.-2</t>
+  </si>
+  <si>
+    <t>P.P. BHASHKARPUR</t>
+  </si>
+  <si>
+    <t>P.P.CHORAULI</t>
+  </si>
+  <si>
+    <t>P.P.RAMPUR CHAMARAHI</t>
+  </si>
+  <si>
+    <t>P.P.MUDAHUVA UTTARI ROOM N.-1</t>
+  </si>
+  <si>
+    <t>P.P.MUDAHUVA UTTARI ROOM N.-2</t>
+  </si>
+  <si>
+    <t>P.P. RAMPUR KALA</t>
+  </si>
+  <si>
+    <t>P.P.BAIRI</t>
+  </si>
+  <si>
+    <t>P.P.MAINPUR</t>
+  </si>
+  <si>
+    <t>P.P.HINAUTI</t>
+  </si>
+  <si>
+    <t>P.P. GADAWA UTTARI</t>
+  </si>
+  <si>
+    <t>P.P. LATHAURA</t>
+  </si>
+  <si>
+    <t>P.P.CHUPPEPUR</t>
+  </si>
+  <si>
+    <t>P.P.AMBAR</t>
+  </si>
+  <si>
+    <t>P.P. KARNAUL</t>
+  </si>
+  <si>
+    <t>P.P.THEKAHA</t>
+  </si>
+  <si>
+    <t>KANYA PATHASHALA SHAHABGANJ ROOM N.-1</t>
+  </si>
+  <si>
+    <t>J.H.SCHOOL SHAHABGANJ ROOM N.-1</t>
+  </si>
+  <si>
+    <t>J.H.SCHOOL SHAHABGANJ ROOM N.-2</t>
+  </si>
+  <si>
+    <t>KANYA PATHASHALA SHAHABGANJ ROOM N.-2</t>
+  </si>
+  <si>
+    <t>P.P. ATAYASTGANJ</t>
+  </si>
+  <si>
+    <t>P.P.DUMARI ROOM N.-1</t>
+  </si>
+  <si>
+    <t>P.P.DUMARI ROOM N.-2</t>
+  </si>
+  <si>
+    <t>P.P.BARAW ROOM N.-1</t>
+  </si>
+  <si>
+    <t>P.P. BARANW ROOM N.-2</t>
+  </si>
+  <si>
+    <t>P.P. KALANI</t>
+  </si>
+  <si>
+    <t>P.P.BADAURA</t>
+  </si>
+  <si>
+    <t>P.P.KANERA</t>
+  </si>
+  <si>
+    <t>P.P. ARARI</t>
+  </si>
+  <si>
+    <t>P.P. BILASPUR</t>
+  </si>
+  <si>
+    <t>P.P.DHUNNUROOM N.-1</t>
+  </si>
+  <si>
+    <t>P.P.DHUNNUROOM N.-2</t>
+  </si>
+  <si>
+    <t>P.P. RASIYA</t>
+  </si>
+  <si>
+    <t>PANCHAYAT BHAWANISAHUL</t>
+  </si>
+  <si>
+    <t>P.P.TIYARI</t>
+  </si>
+  <si>
+    <t>P.P.BIYASAD</t>
+  </si>
+  <si>
+    <t>P.P.DHANAWAL KALA</t>
+  </si>
+  <si>
+    <t>P.P.ISMAILPUR</t>
+  </si>
+  <si>
+    <t>P.P.SEMRAUR</t>
+  </si>
+  <si>
+    <t>P.P.HAJIPUR</t>
+  </si>
+  <si>
+    <t>P.P. PARWATPUR</t>
+  </si>
+  <si>
+    <t>P.P.KUDARA ROOM N.-1</t>
+  </si>
+  <si>
+    <t>P.P.KUDARA ROOM N.-2</t>
+  </si>
+  <si>
+    <t>P.P.PIPARIYA</t>
+  </si>
+  <si>
+    <t>P.P.MAJHAGANWA</t>
+  </si>
+  <si>
+    <t>J.H.SCHOOL BHATWARA KALA</t>
+  </si>
+  <si>
+    <t>P.P.BHATWARA KHURD</t>
+  </si>
+  <si>
+    <t>P.P.BARAUJHI</t>
+  </si>
+  <si>
+    <t>P.P. BIKAPUR</t>
+  </si>
+  <si>
+    <t>P.P. BHALUA BHILAUDI</t>
+  </si>
+  <si>
+    <t>P.P. GOGAHARA</t>
+  </si>
+  <si>
+    <t>P.P. INDRAPURAWA</t>
+  </si>
+  <si>
+    <t>P.P.PACHAWANIYA ROOM N.-1</t>
+  </si>
+  <si>
+    <t>P.P. PACHAWANIYA ROOM N.-2</t>
+  </si>
+  <si>
+    <t>P.P. KERADIH ROOM N.-1</t>
+  </si>
+  <si>
+    <t>P.P. KERADIH ROOM N.-2</t>
+  </si>
+  <si>
+    <t>P.P. LEHARAKHAS</t>
+  </si>
+  <si>
+    <t>P.P. MALDAH</t>
+  </si>
+  <si>
+    <t>P.P. KHAJHARA</t>
+  </si>
+  <si>
+    <t>P.P. DEHARI KALA</t>
+  </si>
+  <si>
+    <t>P.P. KATAWAMAFI</t>
+  </si>
+  <si>
+    <t>P.P. VISHUNPURAWA</t>
+  </si>
+  <si>
+    <t>P.P. MANKAPADA</t>
+  </si>
+  <si>
+    <t>P.P. PADARIYA</t>
+  </si>
+  <si>
+    <t>P.P. PALPUR</t>
+  </si>
+  <si>
+    <t>P.P.AMARA ROOM N.-1</t>
+  </si>
+  <si>
+    <t>P.P.AMARA ROOM N.-2</t>
+  </si>
+  <si>
+    <t>P.P. VIJAYPURAWA</t>
+  </si>
+  <si>
+    <t>P.P. BUDHAWAL</t>
+  </si>
+  <si>
+    <t>P.P. BHAREHATA KAL</t>
+  </si>
+  <si>
+    <t>P.P. SIKANDARPUR ROOM N.-1</t>
+  </si>
+  <si>
+    <t>P.P. SIKANDARPUR ROOM N.-2</t>
+  </si>
+  <si>
+    <t>KANYA J.H.SCHOOL SIKANDARPUR</t>
+  </si>
+  <si>
+    <t>J.H.SCHOOL SIKANDARPUR ROOM N.-1</t>
+  </si>
+  <si>
+    <t>J.H.SCHOOL SIKANDARPUR ROOM N.-2</t>
+  </si>
+  <si>
+    <t>P.P. BHISHAMPUR ROOM N.-1</t>
+  </si>
+  <si>
+    <t>P.P. BHISHAMPUR ROOM N.-2</t>
+  </si>
+  <si>
+    <t>P.P. BHISHAMPUR ROOM N.-3</t>
+  </si>
+  <si>
+    <t>PANCHAYAT BHAWAN BHISHAMPUR</t>
+  </si>
+  <si>
+    <t>J.H.SCHOOL GAYGHAT</t>
+  </si>
+  <si>
+    <t>P.P. ALIPUR BHAGADA</t>
+  </si>
+  <si>
+    <t>P.P. SAHAMATPUR</t>
+  </si>
+  <si>
+    <t>P.P.JIYANPURA</t>
+  </si>
+  <si>
+    <t>P.P. KUSAHI</t>
+  </si>
+  <si>
+    <t>P.P. GANESHPUR</t>
+  </si>
+  <si>
+    <t>P.P. HINAUTI D.</t>
+  </si>
+  <si>
+    <t>P.P. MUBARAKPUR</t>
+  </si>
+  <si>
+    <t>P.P. RATIGARH</t>
+  </si>
+  <si>
+    <t>P.P.KARWADIYA</t>
+  </si>
+  <si>
+    <t>P.P. PIROJPUR</t>
+  </si>
+  <si>
+    <t>P.P. PACHAFEDIYA</t>
+  </si>
+  <si>
+    <t>P.P. RAGHUNATHPUR</t>
+  </si>
+  <si>
+    <t>P.P.TILAURI</t>
+  </si>
+  <si>
+    <t>P.P.SONHUL ROOM N.-1</t>
+  </si>
+  <si>
+    <t>P.P.SONHUL ROOM N.-2</t>
+  </si>
+  <si>
+    <t>A.N..INTER COLLAGE CHAKIA ROOM N.-1</t>
+  </si>
+  <si>
+    <t>A.N.INTER COLLAGE CHAKIA ROOM N.-2</t>
+  </si>
+  <si>
+    <t>J.H.SCHOOL CHAKIA ROOM N.-1</t>
+  </si>
+  <si>
+    <t>J.H.SCHOOL CHAKIA ROOM N.-2</t>
+  </si>
+  <si>
+    <t>P.P. DUHI-SUHI</t>
+  </si>
+  <si>
+    <t>P.P. CHAKIA SECOND</t>
+  </si>
+  <si>
+    <t>KARYALAY VI KHAND CHAKIA ROOM N.-1</t>
+  </si>
+  <si>
+    <t>KARYALAY VI KHAND CHAKIA ROOM N.-2</t>
+  </si>
+  <si>
+    <t>KANYA U.M.V. CHAKIA ROOM N.-1</t>
+  </si>
+  <si>
+    <t>KANYA U.M.V. CHAKIA ROOM N.-2</t>
+  </si>
+  <si>
+    <t>KRAY VIKRAY SAMITI CHAKIA ROOM N.-1</t>
+  </si>
+  <si>
+    <t>KRAY VIKRAY SAMITI CHAKIA ROOM N.-2</t>
+  </si>
+  <si>
+    <t>P.P.CHAKIA FIRST</t>
+  </si>
+  <si>
+    <t>P.P. MUHAMMADABAD ROOM N.-1</t>
+  </si>
+  <si>
+    <t>P.P. MUHAMMADABAD ROOM N.-2</t>
+  </si>
+  <si>
+    <t>P.P. MAGRAUR</t>
+  </si>
+  <si>
+    <t>P.P. GANDHINAGAR ROOM N.-1</t>
+  </si>
+  <si>
+    <t>P.P. GANDHINAGAR ROOM N.-2</t>
+  </si>
+  <si>
+    <t>KISAN U.M.VI.SAIDUPUR ROOM N.-1</t>
+  </si>
+  <si>
+    <t>KISAN U.M.VI. SAIDUPUR ROOM N.-2</t>
+  </si>
+  <si>
+    <t>P.P. SARAIYA</t>
+  </si>
+  <si>
+    <t>P.P. SIHAR</t>
+  </si>
+  <si>
+    <t>J.H.SCHOOL KHARAUJHA</t>
+  </si>
+  <si>
+    <t>A.AN.AM.CENTER BASHADHI</t>
+  </si>
+  <si>
+    <t>PANCHAYAT BHAWAN BASHADHI</t>
+  </si>
+  <si>
+    <t>P.P. SULTANPUR ROOM N.-1</t>
+  </si>
+  <si>
+    <t>P.P. SULTANPUR ROOM N.-2</t>
+  </si>
+  <si>
+    <t>P.P. BANRASIYA</t>
+  </si>
+  <si>
+    <t>P.P. ARJIKALA</t>
+  </si>
+  <si>
+    <t>P.P. ARJIKHURD</t>
+  </si>
+  <si>
+    <t>P.P. BELAWAR</t>
+  </si>
+  <si>
+    <t>P.P. RAMSHALA</t>
+  </si>
+  <si>
+    <t>P.P. USARI</t>
+  </si>
+  <si>
+    <t>P.P. SHAHPUR</t>
+  </si>
+  <si>
+    <t>P.P. DHANNIPUR</t>
+  </si>
+  <si>
+    <t>P.P. KAUDIHAR</t>
+  </si>
+  <si>
+    <t>P.P. GARALA FIRST ROOM N.1</t>
+  </si>
+  <si>
+    <t>P.P. GARALA FIRST ROOM N.2</t>
+  </si>
+  <si>
+    <t>P.P.GARALA SECOND</t>
+  </si>
+  <si>
+    <t>P.P.MAHADEVPUR KALA</t>
+  </si>
+  <si>
+    <t>P.P. BALIYA KHURD ROOM N.-1</t>
+  </si>
+  <si>
+    <t>P.P.BALIYA KHURD ROOM N.-2</t>
+  </si>
+  <si>
+    <t>J.H. SCHOOL BALIYA KALA ROOM N.-1</t>
+  </si>
+  <si>
+    <t>J.H.SCHOOL BALIYA KALA ROOM N.-2</t>
+  </si>
+  <si>
+    <t>P.P.JOGIYA KALA</t>
+  </si>
+  <si>
+    <t>P.P.CHATURIPURKALA</t>
+  </si>
+  <si>
+    <t>P.P.AMARA DAKSHINI</t>
+  </si>
+  <si>
+    <t>P.P.SADAPUR</t>
+  </si>
+  <si>
+    <t>P.P.LATHIYAKALA</t>
+  </si>
+  <si>
+    <t>C.C.S.MA.COLLAGE SHIKARGANJ ROOM NO.1</t>
+  </si>
+  <si>
+    <t>C.C.S.MA.COLLAGE SHIKARGANJ ROOM N.- 2</t>
+  </si>
+  <si>
+    <t>P.P.MUDAHUVA DAKSHINI</t>
+  </si>
+  <si>
+    <t>P.P.BODALPUR</t>
+  </si>
+  <si>
+    <t>P.P.PURANADIH ROOM N.-1</t>
+  </si>
+  <si>
+    <t>P.P.PURANADIH ROOM N.-2</t>
+  </si>
+  <si>
+    <t>P.P.NEWAJGANJ ROOM N.-1</t>
+  </si>
+  <si>
+    <t>P.P.NEWAJGANJ ROOM N.-2</t>
+  </si>
+  <si>
+    <t>P.P.DUBEPURMAFI ROOM N.-1</t>
+  </si>
+  <si>
+    <t>P.P.DUBEPURMAFI ROOM N.-2</t>
+  </si>
+  <si>
+    <t>P.P.BHABHAURA ROOM N.-1</t>
+  </si>
+  <si>
+    <t>P.P.BHABHAURA ROOM N.-2</t>
+  </si>
+  <si>
+    <t>P.P.RAMPUR</t>
+  </si>
+  <si>
+    <t>P.P.MUSAHIBPUR</t>
+  </si>
+  <si>
+    <t>P.P.MUJAFFARPUR ROOMN.-1</t>
+  </si>
+  <si>
+    <t>P.P. MUJAFFARPUR ROOM N.-2</t>
+  </si>
+  <si>
+    <t>P.P. DIREHU ROOM N.-1</t>
+  </si>
+  <si>
+    <t>P.P. DIREHU ROOM N.-2</t>
+  </si>
+  <si>
+    <t>P.P. BAIRA JUNGLE</t>
+  </si>
+  <si>
+    <t>P.P. DODAPUR MAFI</t>
+  </si>
+  <si>
+    <t>P.P. GHURAHUPUR</t>
+  </si>
+  <si>
+    <t>P.P. ISARGODAWA</t>
+  </si>
+  <si>
+    <t>P.P. CHHITTAMPUR</t>
+  </si>
+  <si>
+    <t>P.P. TALA</t>
+  </si>
+  <si>
+    <t>P.P. DHODHANPUR</t>
+  </si>
+  <si>
+    <t>P.P. BANBHISHAMPUR</t>
+  </si>
+  <si>
+    <t>P.P.MUSAKHAND ROOM N.-1</t>
+  </si>
+  <si>
+    <t>P.P.MUSAKHAND ROOM N.-2</t>
+  </si>
+  <si>
+    <t>P.P.MUBARAKPUR ROOM N.-1</t>
+  </si>
+  <si>
+    <t>P.P.MUBARAKPUR ROOM N.-2</t>
+  </si>
+  <si>
+    <t>P.P.JAMSOTI</t>
+  </si>
+  <si>
+    <t>CHANDRA PRABHA DAK BANGLA JAMSOTI</t>
+  </si>
+  <si>
+    <t>P.P. LAUWARI KHURD</t>
+  </si>
+  <si>
+    <t>P.P. NARAKATI</t>
+  </si>
+  <si>
+    <t>P.P. JAYMOHANIPOSTA</t>
+  </si>
+  <si>
+    <t>P.P. MARWATIYA</t>
+  </si>
+  <si>
+    <t>P.P. AMADAHACHARANPUR</t>
+  </si>
+  <si>
+    <t>P.P. GOLABAD</t>
+  </si>
+  <si>
+    <t>P.P. VINAYAKPUR</t>
+  </si>
+  <si>
+    <t>P.P. AMRITPUR</t>
+  </si>
+  <si>
+    <t>P.P. DEVKHAT</t>
+  </si>
+  <si>
+    <t>P.P. AURAWATAND</t>
+  </si>
+  <si>
+    <t>P.P. SEMARSADHOPUR</t>
+  </si>
+  <si>
+    <t>P.P. NONVAT</t>
+  </si>
+  <si>
+    <t>J.H.SCHOOL NAUGARH KHAS</t>
+  </si>
+  <si>
+    <t>P.P. BAGHI ROOM N.-1</t>
+  </si>
+  <si>
+    <t>P.P. BAGHI ROOM N.-2</t>
+  </si>
+  <si>
+    <t>P.P. MALEWAR</t>
+  </si>
+  <si>
+    <t>P.P. SEMARA KUSAHI</t>
+  </si>
+  <si>
+    <t>P.P. RITHIYA</t>
+  </si>
+  <si>
+    <t>P.P. LALATAPUR</t>
+  </si>
+  <si>
+    <t>P.P. DUMARIYA</t>
+  </si>
+  <si>
+    <t>P.P. DEWARI KALA</t>
+  </si>
+  <si>
+    <t>P.P. MAGARAHI</t>
+  </si>
+  <si>
+    <t>P.P. PADHAUTI</t>
+  </si>
+  <si>
+    <t>P.P. CHIKANI</t>
+  </si>
+  <si>
+    <t>P.P. JHUMARIYA</t>
+  </si>
+  <si>
+    <t>P.P. UDITPURSURYA</t>
+  </si>
+  <si>
+    <t>P.P. CHUPPEPUR</t>
+  </si>
+  <si>
+    <t>P.P. BOJH ROOM N.-1</t>
+  </si>
+  <si>
+    <t>P.P. BOJH ROOM N.-2</t>
+  </si>
+  <si>
+    <t>P.P. HARIYABANDH</t>
+  </si>
+  <si>
+    <t>P.P. PIPARAHI</t>
+  </si>
+  <si>
+    <t>P.P. MAJHAGANWA NAI BASTI RAJWAHA</t>
+  </si>
+  <si>
+    <t>P.P. TENDUA</t>
+  </si>
+  <si>
+    <t>R.CH.HS.SCHOOL MAJHAGANWA ROOM N.- 1</t>
+  </si>
+  <si>
+    <t>R.CH.HS.SCHOOL MAJHAGANWA ROOM N.- 2</t>
+  </si>
+  <si>
+    <t>P.P. JAIMOHANI ROOM N.-1</t>
+  </si>
+  <si>
+    <t>P.P. JAIMOHANI ROOM N.-2</t>
+  </si>
+  <si>
+    <t>P.P. VISHESHARPUR</t>
+  </si>
+  <si>
+    <t>P.P. THATHAWA</t>
+  </si>
+  <si>
+    <t>P.P. MAJHAGAI</t>
+  </si>
+  <si>
+    <t>KA.RE.A. MAJHAGAI</t>
+  </si>
+  <si>
+    <t>P.P. DEURA</t>
+  </si>
+  <si>
+    <t>PURVA MADHYAMIK VIDHYALAY BHAISAUDA</t>
+  </si>
+  <si>
+    <t>P.P.JARAHAR</t>
+  </si>
+  <si>
+    <t>P.P. JOMSOT</t>
+  </si>
+  <si>
+    <t>P.P. GAHILA</t>
+  </si>
+  <si>
+    <t>P.P. DHANKUWARI KALA</t>
+  </si>
+  <si>
+    <t>P.P. KESAR</t>
+  </si>
+  <si>
+    <t>P.P. BAIRGADH</t>
+  </si>
+  <si>
+    <t>P.P. NARWADAPUR</t>
+  </si>
+  <si>
+    <t>P.P. HANUMANPUR</t>
+  </si>
+  <si>
+    <t>P.P. JANAKPUR</t>
+  </si>
+  <si>
+    <t>P.P. SONWAR ROOM N.-1</t>
+  </si>
+  <si>
+    <t>P.P. SONWAR ROOM N.-2</t>
+  </si>
+  <si>
+    <t>P.P. SHAMSHERPUR ROOM N.-1</t>
+  </si>
+  <si>
+    <t>P.P. SHAMSHERPUR ROOM N.-2</t>
+  </si>
+  <si>
+    <t>P.P. DEVDATTPUR</t>
+  </si>
+  <si>
+    <t>P.P. HARDAHAWA</t>
+  </si>
+  <si>
+    <t>P.P. PARASAHAWA</t>
+  </si>
+  <si>
+    <t>P.P. CHAKARGHATTA</t>
+  </si>
+  <si>
+    <t>P.P. BARBASPUR</t>
+  </si>
+  <si>
+    <t>P.P. GANGAPUR</t>
+  </si>
+  <si>
+    <t>P.P. BAJARDEEHA</t>
+  </si>
+  <si>
+    <t>P.P. BARAWADEEH</t>
+  </si>
+  <si>
+    <t>P.P.LACHHIMANPUR</t>
+  </si>
+  <si>
+    <t>P.P. BHATAWADIH</t>
+  </si>
+  <si>
+    <t>P.P. PACHKEDIYA</t>
+  </si>
+  <si>
+    <t>P.P. PACHKEDIYA ROOM NO. 392</t>
+  </si>
+  <si>
+    <t>P.P. PACHKEDIYA ROOM ROOM NO. 393</t>
+  </si>
+  <si>
+    <t>P.P. PACHKEDIYA ROOM ROOM ROOM NO. 394</t>
+  </si>
+  <si>
+    <t>P.P. PACHKEDIYA ROOM ROOM ROOM ROOM NO. 395</t>
+  </si>
+  <si>
+    <t>P.P. PACHKEDIYA ROOM ROOM ROOM ROOM ROOM NO. 396</t>
+  </si>
+  <si>
+    <t>P.P. PACHKEDIYA ROOM ROOM ROOM ROOM ROOM ROOM NO. 397</t>
+  </si>
+  <si>
+    <t>P.P. PACHKEDIYA ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 398</t>
+  </si>
+  <si>
+    <t>P.P. PACHKEDIYA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 399</t>
+  </si>
+  <si>
+    <t>P.P. PACHKEDIYA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 400</t>
+  </si>
+  <si>
+    <t>P.P. PACHKEDIYA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 401</t>
+  </si>
+  <si>
+    <t>P.P. PACHKEDIYA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 402</t>
+  </si>
+  <si>
+    <t>P.P. PACHKEDIYA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 403</t>
+  </si>
+  <si>
+    <t>P.P. PACHKEDIYA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 404</t>
+  </si>
+  <si>
+    <t>P.P. PACHKEDIYA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 405</t>
+  </si>
+  <si>
+    <t>P.P. PACHKEDIYA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 406</t>
+  </si>
+  <si>
+    <t>P.P. PACHKEDIYA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 407</t>
+  </si>
+  <si>
+    <t>P.P. PACHKEDIYA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 408</t>
+  </si>
+  <si>
+    <t>P.P. PACHKEDIYA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 409</t>
+  </si>
+  <si>
+    <t>P.P. PACHKEDIYA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 410</t>
+  </si>
+  <si>
+    <t>P.P. PACHKEDIYA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 411</t>
+  </si>
+  <si>
+    <t>P.P. PACHKEDIYA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 412</t>
+  </si>
+  <si>
+    <t>P.P. PACHKEDIYA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 413</t>
+  </si>
+  <si>
+    <t>P.P. PACHKEDIYA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 414</t>
+  </si>
+  <si>
+    <t>P.P. PACHKEDIYA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 415</t>
+  </si>
+  <si>
+    <t>P.P. PACHKEDIYA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 416</t>
+  </si>
+  <si>
+    <t>P.P. PACHKEDIYA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 417</t>
+  </si>
+  <si>
+    <t>P.P. PACHKEDIYA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 418</t>
+  </si>
+  <si>
+    <t>P.P. PACHKEDIYA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 419</t>
+  </si>
+  <si>
+    <t>P.P. PACHKEDIYA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 420</t>
+  </si>
+  <si>
+    <t>P.P. PACHKEDIYA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 421</t>
+  </si>
+  <si>
+    <t>P.P. PACHKEDIYA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 422</t>
+  </si>
+  <si>
+    <t>P.P. PACHKEDIYA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 423</t>
+  </si>
+  <si>
+    <t>P.P. PACHKEDIYA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 424</t>
+  </si>
+  <si>
+    <t>P.P. PACHKEDIYA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 425</t>
+  </si>
+  <si>
+    <t>P.P. PACHKEDIYA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 426</t>
+  </si>
+  <si>
+    <t>P.P. PACHKEDIYA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 427</t>
+  </si>
+  <si>
+    <t>P.P. PACHKEDIYA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 428</t>
+  </si>
+  <si>
+    <t>P.P. PACHKEDIYA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 429</t>
+  </si>
+  <si>
+    <t>P.P. PACHKEDIYA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 430</t>
+  </si>
+  <si>
+    <t>P.P. PACHKEDIYA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 431</t>
+  </si>
+  <si>
+    <t>P.P. PACHKEDIYA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 432</t>
+  </si>
+  <si>
+    <t>P.P. PACHKEDIYA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 433</t>
+  </si>
+  <si>
+    <t>P.P. PACHKEDIYA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 434</t>
+  </si>
+  <si>
+    <t>P.P. PACHKEDIYA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 435</t>
+  </si>
+  <si>
+    <t>P.P. PACHKEDIYA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 436</t>
+  </si>
+  <si>
+    <t>P.P. PACHKEDIYA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 437</t>
+  </si>
+  <si>
+    <t>P.P. PACHKEDIYA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 438</t>
+  </si>
+  <si>
+    <t>P.P. PACHKEDIYA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 439</t>
+  </si>
+  <si>
+    <t>P.P. PACHKEDIYA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 440</t>
+  </si>
+  <si>
+    <t>P.P. PACHKEDIYA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 441</t>
+  </si>
+  <si>
+    <t>P.P. PACHKEDIYA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 442</t>
+  </si>
+  <si>
+    <t>P.P. PACHKEDIYA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 443</t>
+  </si>
+  <si>
+    <t>P.P. PACHKEDIYA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 444</t>
+  </si>
+  <si>
+    <t>P.P. PACHKEDIYA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 445</t>
+  </si>
+  <si>
+    <t>P.P. PACHKEDIYA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 446</t>
+  </si>
+  <si>
+    <t>P.P. PACHKEDIYA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 447</t>
+  </si>
+  <si>
+    <t>P.P. PACHKEDIYA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 448</t>
+  </si>
+  <si>
+    <t>P.P. PACHKEDIYA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 449</t>
+  </si>
+  <si>
+    <t>P.P. PACHKEDIYA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 450</t>
+  </si>
+  <si>
+    <t>P.P. PACHKEDIYA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 451</t>
+  </si>
+  <si>
+    <t>P.P. PACHKEDIYA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 452</t>
+  </si>
+  <si>
+    <t>P.P. PACHKEDIYA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 453</t>
+  </si>
+  <si>
+    <t>P.P. PACHKEDIYA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 454</t>
+  </si>
+  <si>
+    <t>P.P. PACHKEDIYA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 455</t>
+  </si>
+  <si>
+    <t>P.P. PACHKEDIYA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 456</t>
+  </si>
+  <si>
+    <t>P.P. PACHKEDIYA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 457</t>
+  </si>
+  <si>
+    <t>P.P. PACHKEDIYA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 458</t>
+  </si>
+  <si>
+    <t>P.P. PACHKEDIYA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 459</t>
+  </si>
+  <si>
+    <t>P.P. PACHKEDIYA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 460</t>
   </si>
   <si>
     <t>TOTAL ELECTORS</t>
@@ -827,8 +1526,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -844,7 +1551,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -852,12 +1559,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1156,79 +1881,145 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:23">
-      <c r="A1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:23">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>248</v>
+        <v>481</v>
       </c>
       <c r="D2" t="s">
-        <v>249</v>
+        <v>482</v>
       </c>
       <c r="E2" t="s">
-        <v>250</v>
+        <v>483</v>
       </c>
       <c r="F2" t="s">
-        <v>251</v>
+        <v>484</v>
       </c>
       <c r="G2" t="s">
-        <v>252</v>
+        <v>485</v>
       </c>
       <c r="H2" t="s">
-        <v>253</v>
+        <v>486</v>
       </c>
       <c r="I2" t="s">
-        <v>254</v>
+        <v>487</v>
       </c>
       <c r="J2" t="s">
-        <v>255</v>
+        <v>488</v>
       </c>
       <c r="K2" t="s">
-        <v>256</v>
+        <v>489</v>
       </c>
       <c r="L2" t="s">
-        <v>257</v>
+        <v>490</v>
       </c>
       <c r="M2" t="s">
-        <v>258</v>
+        <v>491</v>
       </c>
       <c r="N2" t="s">
-        <v>259</v>
+        <v>492</v>
       </c>
       <c r="O2" t="s">
-        <v>260</v>
+        <v>493</v>
       </c>
       <c r="P2" t="s">
-        <v>261</v>
+        <v>494</v>
       </c>
       <c r="Q2" t="s">
-        <v>262</v>
+        <v>495</v>
       </c>
       <c r="R2" t="s">
-        <v>263</v>
+        <v>496</v>
       </c>
       <c r="S2" t="s">
-        <v>264</v>
+        <v>497</v>
       </c>
       <c r="T2" t="s">
-        <v>265</v>
+        <v>498</v>
       </c>
       <c r="U2" t="s">
-        <v>266</v>
+        <v>499</v>
       </c>
       <c r="V2" t="s">
-        <v>267</v>
+        <v>500</v>
       </c>
       <c r="W2" t="s">
-        <v>268</v>
+        <v>501</v>
       </c>
     </row>
     <row r="3" spans="1:23">
@@ -1236,7 +2027,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C3">
         <v>745</v>
@@ -1307,7 +2098,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C4">
         <v>1172</v>
@@ -1378,7 +2169,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="C5">
         <v>755</v>
@@ -1449,7 +2240,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="C6">
         <v>827</v>
@@ -1520,7 +2311,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="C7">
         <v>779</v>
@@ -1591,7 +2382,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="C8">
         <v>1043</v>
@@ -1662,7 +2453,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C9">
         <v>943</v>
@@ -1733,7 +2524,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="C10">
         <v>668</v>
@@ -1804,7 +2595,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="C11">
         <v>857</v>
@@ -1875,7 +2666,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="C12">
         <v>835</v>
@@ -1946,7 +2737,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="C13">
         <v>498</v>
@@ -2017,7 +2808,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="C14">
         <v>946</v>
@@ -2088,7 +2879,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="C15">
         <v>1013</v>
@@ -2159,7 +2950,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="C16">
         <v>686</v>
@@ -2230,7 +3021,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="C17">
         <v>970</v>
@@ -2301,7 +3092,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="C18">
         <v>785</v>
@@ -2372,7 +3163,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="C19">
         <v>892</v>
@@ -2443,7 +3234,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="C20">
         <v>475</v>
@@ -2514,7 +3305,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="C21">
         <v>935</v>
@@ -2585,7 +3376,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="C22">
         <v>760</v>
@@ -2656,7 +3447,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="C23">
         <v>1134</v>
@@ -2727,7 +3518,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="C24">
         <v>767</v>
@@ -2798,7 +3589,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="C25">
         <v>690</v>
@@ -2869,7 +3660,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="C26">
         <v>783</v>
@@ -2940,7 +3731,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="C27">
         <v>715</v>
@@ -3011,7 +3802,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="C28">
         <v>640</v>
@@ -3082,7 +3873,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="C29">
         <v>633</v>
@@ -3153,7 +3944,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="C30">
         <v>811</v>
@@ -3224,7 +4015,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="C31">
         <v>451</v>
@@ -3295,7 +4086,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="C32">
         <v>1014</v>
@@ -3366,7 +4157,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="C33">
         <v>986</v>
@@ -3437,7 +4228,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C34">
         <v>715</v>
@@ -3508,7 +4299,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="C35">
         <v>870</v>
@@ -3579,7 +4370,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="C36">
         <v>951</v>
@@ -3650,7 +4441,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="C37">
         <v>956</v>
@@ -3721,7 +4512,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="C38">
         <v>854</v>
@@ -3792,7 +4583,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="C39">
         <v>670</v>
@@ -3863,7 +4654,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="C40">
         <v>920</v>
@@ -3934,7 +4725,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>10</v>
+        <v>63</v>
       </c>
       <c r="C41">
         <v>1149</v>
@@ -4005,7 +4796,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>37</v>
+        <v>64</v>
       </c>
       <c r="C42">
         <v>1109</v>
@@ -4076,7 +4867,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="C43">
         <v>715</v>
@@ -4147,7 +4938,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="C44">
         <v>740</v>
@@ -4218,7 +5009,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="C45">
         <v>1128</v>
@@ -4289,7 +5080,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="C46">
         <v>833</v>
@@ -4360,7 +5151,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="C47">
         <v>1160</v>
@@ -4431,7 +5222,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="C48">
         <v>775</v>
@@ -4502,7 +5293,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="C49">
         <v>1076</v>
@@ -4573,7 +5364,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="C50">
         <v>442</v>
@@ -4644,7 +5435,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>46</v>
+        <v>73</v>
       </c>
       <c r="C51">
         <v>611</v>
@@ -4715,7 +5506,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="C52">
         <v>822</v>
@@ -4786,7 +5577,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="C53">
         <v>732</v>
@@ -4857,7 +5648,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="C54">
         <v>533</v>
@@ -4928,7 +5719,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="C55">
         <v>839</v>
@@ -4999,7 +5790,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>22</v>
+        <v>78</v>
       </c>
       <c r="C56">
         <v>1054</v>
@@ -5070,7 +5861,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>23</v>
+        <v>79</v>
       </c>
       <c r="C57">
         <v>911</v>
@@ -5141,7 +5932,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="C58">
         <v>1158</v>
@@ -5212,7 +6003,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>52</v>
+        <v>81</v>
       </c>
       <c r="C59">
         <v>1009</v>
@@ -5283,7 +6074,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>29</v>
+        <v>82</v>
       </c>
       <c r="C60">
         <v>966</v>
@@ -5354,7 +6145,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>53</v>
+        <v>83</v>
       </c>
       <c r="C61">
         <v>1033</v>
@@ -5425,7 +6216,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="C62">
         <v>1046</v>
@@ -5496,7 +6287,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>9</v>
+        <v>85</v>
       </c>
       <c r="C63">
         <v>649</v>
@@ -5567,7 +6358,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="C64">
         <v>725</v>
@@ -5638,7 +6429,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>55</v>
+        <v>87</v>
       </c>
       <c r="C65">
         <v>748</v>
@@ -5709,7 +6500,7 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>56</v>
+        <v>88</v>
       </c>
       <c r="C66">
         <v>1001</v>
@@ -5780,7 +6571,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>57</v>
+        <v>89</v>
       </c>
       <c r="C67">
         <v>985</v>
@@ -5851,7 +6642,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>58</v>
+        <v>90</v>
       </c>
       <c r="C68">
         <v>719</v>
@@ -5922,7 +6713,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>59</v>
+        <v>91</v>
       </c>
       <c r="C69">
         <v>470</v>
@@ -5993,7 +6784,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>60</v>
+        <v>92</v>
       </c>
       <c r="C70">
         <v>982</v>
@@ -6064,7 +6855,7 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="C71">
         <v>1039</v>
@@ -6135,7 +6926,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>9</v>
+        <v>94</v>
       </c>
       <c r="C72">
         <v>714</v>
@@ -6206,7 +6997,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>45</v>
+        <v>95</v>
       </c>
       <c r="C73">
         <v>1152</v>
@@ -6277,7 +7068,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>62</v>
+        <v>96</v>
       </c>
       <c r="C74">
         <v>622</v>
@@ -6348,7 +7139,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>63</v>
+        <v>97</v>
       </c>
       <c r="C75">
         <v>648</v>
@@ -6419,7 +7210,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>64</v>
+        <v>98</v>
       </c>
       <c r="C76">
         <v>442</v>
@@ -6490,7 +7281,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="C77">
         <v>1030</v>
@@ -6561,7 +7352,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="C78">
         <v>654</v>
@@ -6632,7 +7423,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>66</v>
+        <v>101</v>
       </c>
       <c r="C79">
         <v>995</v>
@@ -6703,7 +7494,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>4</v>
+        <v>102</v>
       </c>
       <c r="C80">
         <v>1011</v>
@@ -6774,7 +7565,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>5</v>
+        <v>103</v>
       </c>
       <c r="C81">
         <v>480</v>
@@ -6845,7 +7636,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="C82">
         <v>489</v>
@@ -6916,7 +7707,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>67</v>
+        <v>105</v>
       </c>
       <c r="C83">
         <v>808</v>
@@ -6987,7 +7778,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>68</v>
+        <v>106</v>
       </c>
       <c r="C84">
         <v>593</v>
@@ -7058,7 +7849,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>69</v>
+        <v>107</v>
       </c>
       <c r="C85">
         <v>616</v>
@@ -7129,7 +7920,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>17</v>
+        <v>108</v>
       </c>
       <c r="C86">
         <v>1044</v>
@@ -7200,7 +7991,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>70</v>
+        <v>109</v>
       </c>
       <c r="C87">
         <v>828</v>
@@ -7271,7 +8062,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>71</v>
+        <v>110</v>
       </c>
       <c r="C88">
         <v>684</v>
@@ -7342,7 +8133,7 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>72</v>
+        <v>111</v>
       </c>
       <c r="C89">
         <v>706</v>
@@ -7413,7 +8204,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>73</v>
+        <v>112</v>
       </c>
       <c r="C90">
         <v>581</v>
@@ -7484,7 +8275,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>60</v>
+        <v>113</v>
       </c>
       <c r="C91">
         <v>746</v>
@@ -7555,7 +8346,7 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>61</v>
+        <v>114</v>
       </c>
       <c r="C92">
         <v>780</v>
@@ -7626,7 +8417,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>59</v>
+        <v>115</v>
       </c>
       <c r="C93">
         <v>872</v>
@@ -7697,7 +8488,7 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>74</v>
+        <v>116</v>
       </c>
       <c r="C94">
         <v>746</v>
@@ -7768,7 +8559,7 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>75</v>
+        <v>117</v>
       </c>
       <c r="C95">
         <v>938</v>
@@ -7839,7 +8630,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>64</v>
+        <v>118</v>
       </c>
       <c r="C96">
         <v>626</v>
@@ -7910,7 +8701,7 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>65</v>
+        <v>119</v>
       </c>
       <c r="C97">
         <v>632</v>
@@ -7981,7 +8772,7 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>76</v>
+        <v>120</v>
       </c>
       <c r="C98">
         <v>948</v>
@@ -8052,7 +8843,7 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>77</v>
+        <v>121</v>
       </c>
       <c r="C99">
         <v>1000</v>
@@ -8123,7 +8914,7 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>3</v>
+        <v>122</v>
       </c>
       <c r="C100">
         <v>1141</v>
@@ -8194,7 +8985,7 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>51</v>
+        <v>123</v>
       </c>
       <c r="C101">
         <v>1135</v>
@@ -8265,7 +9056,7 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>78</v>
+        <v>124</v>
       </c>
       <c r="C102">
         <v>736</v>
@@ -8336,7 +9127,7 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>79</v>
+        <v>125</v>
       </c>
       <c r="C103">
         <v>721</v>
@@ -8407,7 +9198,7 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>80</v>
+        <v>126</v>
       </c>
       <c r="C104">
         <v>710</v>
@@ -8478,7 +9269,7 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>81</v>
+        <v>127</v>
       </c>
       <c r="C105">
         <v>611</v>
@@ -8549,7 +9340,7 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>82</v>
+        <v>128</v>
       </c>
       <c r="C106">
         <v>733</v>
@@ -8620,7 +9411,7 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>83</v>
+        <v>129</v>
       </c>
       <c r="C107">
         <v>570</v>
@@ -8691,7 +9482,7 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>84</v>
+        <v>130</v>
       </c>
       <c r="C108">
         <v>1117</v>
@@ -8762,7 +9553,7 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>85</v>
+        <v>131</v>
       </c>
       <c r="C109">
         <v>1000</v>
@@ -8833,7 +9624,7 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>52</v>
+        <v>132</v>
       </c>
       <c r="C110">
         <v>935</v>
@@ -8904,7 +9695,7 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>86</v>
+        <v>133</v>
       </c>
       <c r="C111">
         <v>736</v>
@@ -8975,7 +9766,7 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>45</v>
+        <v>134</v>
       </c>
       <c r="C112">
         <v>742</v>
@@ -9046,7 +9837,7 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>51</v>
+        <v>135</v>
       </c>
       <c r="C113">
         <v>811</v>
@@ -9117,7 +9908,7 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>54</v>
+        <v>136</v>
       </c>
       <c r="C114">
         <v>1162</v>
@@ -9188,7 +9979,7 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>56</v>
+        <v>137</v>
       </c>
       <c r="C115">
         <v>1113</v>
@@ -9259,7 +10050,7 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>37</v>
+        <v>138</v>
       </c>
       <c r="C116">
         <v>516</v>
@@ -9330,7 +10121,7 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>87</v>
+        <v>139</v>
       </c>
       <c r="C117">
         <v>1185</v>
@@ -9401,7 +10192,7 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>88</v>
+        <v>140</v>
       </c>
       <c r="C118">
         <v>739</v>
@@ -9472,7 +10263,7 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>50</v>
+        <v>141</v>
       </c>
       <c r="C119">
         <v>1075</v>
@@ -9543,7 +10334,7 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>89</v>
+        <v>142</v>
       </c>
       <c r="C120">
         <v>662</v>
@@ -9614,7 +10405,7 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>90</v>
+        <v>143</v>
       </c>
       <c r="C121">
         <v>612</v>
@@ -9685,7 +10476,7 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>91</v>
+        <v>144</v>
       </c>
       <c r="C122">
         <v>638</v>
@@ -9756,7 +10547,7 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>75</v>
+        <v>145</v>
       </c>
       <c r="C123">
         <v>861</v>
@@ -9827,7 +10618,7 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>79</v>
+        <v>146</v>
       </c>
       <c r="C124">
         <v>697</v>
@@ -9898,7 +10689,7 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>92</v>
+        <v>147</v>
       </c>
       <c r="C125">
         <v>857</v>
@@ -9969,7 +10760,7 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>93</v>
+        <v>148</v>
       </c>
       <c r="C126">
         <v>831</v>
@@ -10040,7 +10831,7 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>94</v>
+        <v>149</v>
       </c>
       <c r="C127">
         <v>862</v>
@@ -10111,7 +10902,7 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>95</v>
+        <v>150</v>
       </c>
       <c r="C128">
         <v>1115</v>
@@ -10182,7 +10973,7 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>54</v>
+        <v>151</v>
       </c>
       <c r="C129">
         <v>1039</v>
@@ -10253,7 +11044,7 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>56</v>
+        <v>152</v>
       </c>
       <c r="C130">
         <v>957</v>
@@ -10324,7 +11115,7 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>96</v>
+        <v>153</v>
       </c>
       <c r="C131">
         <v>1188</v>
@@ -10395,7 +11186,7 @@
         <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>97</v>
+        <v>154</v>
       </c>
       <c r="C132">
         <v>767</v>
@@ -10466,7 +11257,7 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>98</v>
+        <v>155</v>
       </c>
       <c r="C133">
         <v>460</v>
@@ -10537,7 +11328,7 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>79</v>
+        <v>156</v>
       </c>
       <c r="C134">
         <v>889</v>
@@ -10608,7 +11399,7 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>99</v>
+        <v>157</v>
       </c>
       <c r="C135">
         <v>1121</v>
@@ -10679,7 +11470,7 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>100</v>
+        <v>158</v>
       </c>
       <c r="C136">
         <v>398</v>
@@ -10750,7 +11541,7 @@
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>54</v>
+        <v>159</v>
       </c>
       <c r="C137">
         <v>682</v>
@@ -10821,7 +11612,7 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>56</v>
+        <v>160</v>
       </c>
       <c r="C138">
         <v>759</v>
@@ -10892,7 +11683,7 @@
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>101</v>
+        <v>161</v>
       </c>
       <c r="C139">
         <v>943</v>
@@ -10963,7 +11754,7 @@
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>72</v>
+        <v>162</v>
       </c>
       <c r="C140">
         <v>1048</v>
@@ -11034,7 +11825,7 @@
         <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>95</v>
+        <v>163</v>
       </c>
       <c r="C141">
         <v>721</v>
@@ -11105,7 +11896,7 @@
         <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>102</v>
+        <v>164</v>
       </c>
       <c r="C142">
         <v>812</v>
@@ -11176,7 +11967,7 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="C143">
         <v>770</v>
@@ -11247,7 +12038,7 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>104</v>
+        <v>166</v>
       </c>
       <c r="C144">
         <v>837</v>
@@ -11318,7 +12109,7 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>54</v>
+        <v>167</v>
       </c>
       <c r="C145">
         <v>967</v>
@@ -11389,7 +12180,7 @@
         <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>105</v>
+        <v>168</v>
       </c>
       <c r="C146">
         <v>1025</v>
@@ -11460,7 +12251,7 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>56</v>
+        <v>169</v>
       </c>
       <c r="C147">
         <v>729</v>
@@ -11531,7 +12322,7 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>79</v>
+        <v>170</v>
       </c>
       <c r="C148">
         <v>731</v>
@@ -11602,7 +12393,7 @@
         <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>103</v>
+        <v>171</v>
       </c>
       <c r="C149">
         <v>621</v>
@@ -11673,7 +12464,7 @@
         <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>95</v>
+        <v>172</v>
       </c>
       <c r="C150">
         <v>1018</v>
@@ -11744,7 +12535,7 @@
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>106</v>
+        <v>173</v>
       </c>
       <c r="C151">
         <v>539</v>
@@ -11815,7 +12606,7 @@
         <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>107</v>
+        <v>174</v>
       </c>
       <c r="C152">
         <v>1027</v>
@@ -11886,7 +12677,7 @@
         <v>151</v>
       </c>
       <c r="B153" t="s">
-        <v>108</v>
+        <v>175</v>
       </c>
       <c r="C153">
         <v>1126</v>
@@ -11957,7 +12748,7 @@
         <v>152</v>
       </c>
       <c r="B154" t="s">
-        <v>109</v>
+        <v>176</v>
       </c>
       <c r="C154">
         <v>1159</v>
@@ -12028,7 +12819,7 @@
         <v>153</v>
       </c>
       <c r="B155" t="s">
-        <v>80</v>
+        <v>177</v>
       </c>
       <c r="C155">
         <v>721</v>
@@ -12099,7 +12890,7 @@
         <v>154</v>
       </c>
       <c r="B156" t="s">
-        <v>81</v>
+        <v>178</v>
       </c>
       <c r="C156">
         <v>761</v>
@@ -12170,7 +12961,7 @@
         <v>155</v>
       </c>
       <c r="B157" t="s">
-        <v>110</v>
+        <v>179</v>
       </c>
       <c r="C157">
         <v>561</v>
@@ -12241,7 +13032,7 @@
         <v>156</v>
       </c>
       <c r="B158" t="s">
-        <v>101</v>
+        <v>180</v>
       </c>
       <c r="C158">
         <v>781</v>
@@ -12312,7 +13103,7 @@
         <v>157</v>
       </c>
       <c r="B159" t="s">
-        <v>72</v>
+        <v>181</v>
       </c>
       <c r="C159">
         <v>663</v>
@@ -12383,7 +13174,7 @@
         <v>158</v>
       </c>
       <c r="B160" t="s">
-        <v>111</v>
+        <v>182</v>
       </c>
       <c r="C160">
         <v>1043</v>
@@ -12454,7 +13245,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="C161">
         <v>790</v>
@@ -12525,7 +13316,7 @@
         <v>160</v>
       </c>
       <c r="B162" t="s">
-        <v>113</v>
+        <v>183</v>
       </c>
       <c r="C162">
         <v>1213</v>
@@ -12596,7 +13387,7 @@
         <v>161</v>
       </c>
       <c r="B163" t="s">
-        <v>114</v>
+        <v>184</v>
       </c>
       <c r="C163">
         <v>1071</v>
@@ -12667,7 +13458,7 @@
         <v>162</v>
       </c>
       <c r="B164" t="s">
-        <v>115</v>
+        <v>185</v>
       </c>
       <c r="C164">
         <v>472</v>
@@ -12738,7 +13529,7 @@
         <v>163</v>
       </c>
       <c r="B165" t="s">
-        <v>116</v>
+        <v>186</v>
       </c>
       <c r="C165">
         <v>777</v>
@@ -12809,7 +13600,7 @@
         <v>164</v>
       </c>
       <c r="B166" t="s">
-        <v>73</v>
+        <v>187</v>
       </c>
       <c r="C166">
         <v>1046</v>
@@ -12880,7 +13671,7 @@
         <v>165</v>
       </c>
       <c r="B167" t="s">
-        <v>117</v>
+        <v>188</v>
       </c>
       <c r="C167">
         <v>1054</v>
@@ -12951,7 +13742,7 @@
         <v>166</v>
       </c>
       <c r="B168" t="s">
-        <v>118</v>
+        <v>189</v>
       </c>
       <c r="C168">
         <v>745</v>
@@ -13022,7 +13813,7 @@
         <v>167</v>
       </c>
       <c r="B169" t="s">
-        <v>54</v>
+        <v>190</v>
       </c>
       <c r="C169">
         <v>692</v>
@@ -13093,7 +13884,7 @@
         <v>168</v>
       </c>
       <c r="B170" t="s">
-        <v>56</v>
+        <v>191</v>
       </c>
       <c r="C170">
         <v>682</v>
@@ -13164,7 +13955,7 @@
         <v>169</v>
       </c>
       <c r="B171" t="s">
-        <v>119</v>
+        <v>192</v>
       </c>
       <c r="C171">
         <v>679</v>
@@ -13235,7 +14026,7 @@
         <v>170</v>
       </c>
       <c r="B172" t="s">
-        <v>120</v>
+        <v>193</v>
       </c>
       <c r="C172">
         <v>678</v>
@@ -13306,7 +14097,7 @@
         <v>171</v>
       </c>
       <c r="B173" t="s">
-        <v>97</v>
+        <v>194</v>
       </c>
       <c r="C173">
         <v>797</v>
@@ -13377,7 +14168,7 @@
         <v>172</v>
       </c>
       <c r="B174" t="s">
-        <v>98</v>
+        <v>195</v>
       </c>
       <c r="C174">
         <v>816</v>
@@ -13448,7 +14239,7 @@
         <v>173</v>
       </c>
       <c r="B175" t="s">
-        <v>121</v>
+        <v>196</v>
       </c>
       <c r="C175">
         <v>1024</v>
@@ -13519,7 +14310,7 @@
         <v>174</v>
       </c>
       <c r="B176" t="s">
-        <v>101</v>
+        <v>197</v>
       </c>
       <c r="C176">
         <v>986</v>
@@ -13590,7 +14381,7 @@
         <v>175</v>
       </c>
       <c r="B177" t="s">
-        <v>72</v>
+        <v>198</v>
       </c>
       <c r="C177">
         <v>932</v>
@@ -13661,7 +14452,7 @@
         <v>176</v>
       </c>
       <c r="B178" t="s">
-        <v>122</v>
+        <v>199</v>
       </c>
       <c r="C178">
         <v>697</v>
@@ -13732,7 +14523,7 @@
         <v>177</v>
       </c>
       <c r="B179" t="s">
-        <v>95</v>
+        <v>200</v>
       </c>
       <c r="C179">
         <v>1132</v>
@@ -13803,7 +14594,7 @@
         <v>178</v>
       </c>
       <c r="B180" t="s">
-        <v>123</v>
+        <v>201</v>
       </c>
       <c r="C180">
         <v>831</v>
@@ -13874,7 +14665,7 @@
         <v>179</v>
       </c>
       <c r="B181" t="s">
-        <v>124</v>
+        <v>202</v>
       </c>
       <c r="C181">
         <v>877</v>
@@ -13945,7 +14736,7 @@
         <v>180</v>
       </c>
       <c r="B182" t="s">
-        <v>125</v>
+        <v>203</v>
       </c>
       <c r="C182">
         <v>900</v>
@@ -14016,7 +14807,7 @@
         <v>181</v>
       </c>
       <c r="B183" t="s">
-        <v>126</v>
+        <v>204</v>
       </c>
       <c r="C183">
         <v>729</v>
@@ -14087,7 +14878,7 @@
         <v>182</v>
       </c>
       <c r="B184" t="s">
-        <v>51</v>
+        <v>205</v>
       </c>
       <c r="C184">
         <v>656</v>
@@ -14158,7 +14949,7 @@
         <v>183</v>
       </c>
       <c r="B185" t="s">
-        <v>95</v>
+        <v>206</v>
       </c>
       <c r="C185">
         <v>1083</v>
@@ -14229,7 +15020,7 @@
         <v>184</v>
       </c>
       <c r="B186" t="s">
-        <v>127</v>
+        <v>207</v>
       </c>
       <c r="C186">
         <v>802</v>
@@ -14300,7 +15091,7 @@
         <v>185</v>
       </c>
       <c r="B187" t="s">
-        <v>128</v>
+        <v>208</v>
       </c>
       <c r="C187">
         <v>1076</v>
@@ -14371,7 +15162,7 @@
         <v>186</v>
       </c>
       <c r="B188" t="s">
-        <v>84</v>
+        <v>209</v>
       </c>
       <c r="C188">
         <v>1173</v>
@@ -14442,7 +15233,7 @@
         <v>187</v>
       </c>
       <c r="B189" t="s">
-        <v>121</v>
+        <v>210</v>
       </c>
       <c r="C189">
         <v>1170</v>
@@ -14513,7 +15304,7 @@
         <v>188</v>
       </c>
       <c r="B190" t="s">
-        <v>73</v>
+        <v>211</v>
       </c>
       <c r="C190">
         <v>891</v>
@@ -14584,7 +15375,7 @@
         <v>189</v>
       </c>
       <c r="B191" t="s">
-        <v>103</v>
+        <v>212</v>
       </c>
       <c r="C191">
         <v>344</v>
@@ -14655,7 +15446,7 @@
         <v>190</v>
       </c>
       <c r="B192" t="s">
-        <v>54</v>
+        <v>213</v>
       </c>
       <c r="C192">
         <v>668</v>
@@ -14726,7 +15517,7 @@
         <v>191</v>
       </c>
       <c r="B193" t="s">
-        <v>56</v>
+        <v>214</v>
       </c>
       <c r="C193">
         <v>672</v>
@@ -14797,7 +15588,7 @@
         <v>192</v>
       </c>
       <c r="B194" t="s">
-        <v>84</v>
+        <v>215</v>
       </c>
       <c r="C194">
         <v>859</v>
@@ -14868,7 +15659,7 @@
         <v>193</v>
       </c>
       <c r="B195" t="s">
-        <v>52</v>
+        <v>216</v>
       </c>
       <c r="C195">
         <v>782</v>
@@ -14939,7 +15730,7 @@
         <v>194</v>
       </c>
       <c r="B196" t="s">
-        <v>129</v>
+        <v>217</v>
       </c>
       <c r="C196">
         <v>752</v>
@@ -15010,7 +15801,7 @@
         <v>195</v>
       </c>
       <c r="B197" t="s">
-        <v>130</v>
+        <v>218</v>
       </c>
       <c r="C197">
         <v>936</v>
@@ -15081,7 +15872,7 @@
         <v>196</v>
       </c>
       <c r="B198" t="s">
-        <v>131</v>
+        <v>219</v>
       </c>
       <c r="C198">
         <v>758</v>
@@ -15152,7 +15943,7 @@
         <v>197</v>
       </c>
       <c r="B199" t="s">
-        <v>86</v>
+        <v>220</v>
       </c>
       <c r="C199">
         <v>626</v>
@@ -15223,7 +16014,7 @@
         <v>198</v>
       </c>
       <c r="B200" t="s">
-        <v>132</v>
+        <v>221</v>
       </c>
       <c r="C200">
         <v>630</v>
@@ -15294,7 +16085,7 @@
         <v>199</v>
       </c>
       <c r="B201" t="s">
-        <v>133</v>
+        <v>222</v>
       </c>
       <c r="C201">
         <v>696</v>
@@ -15365,7 +16156,7 @@
         <v>200</v>
       </c>
       <c r="B202" t="s">
-        <v>134</v>
+        <v>223</v>
       </c>
       <c r="C202">
         <v>632</v>
@@ -15436,7 +16227,7 @@
         <v>201</v>
       </c>
       <c r="B203" t="s">
-        <v>97</v>
+        <v>224</v>
       </c>
       <c r="C203">
         <v>993</v>
@@ -15507,7 +16298,7 @@
         <v>202</v>
       </c>
       <c r="B204" t="s">
-        <v>98</v>
+        <v>225</v>
       </c>
       <c r="C204">
         <v>924</v>
@@ -15578,7 +16369,7 @@
         <v>203</v>
       </c>
       <c r="B205" t="s">
-        <v>99</v>
+        <v>226</v>
       </c>
       <c r="C205">
         <v>1033</v>
@@ -15649,7 +16440,7 @@
         <v>204</v>
       </c>
       <c r="B206" t="s">
-        <v>100</v>
+        <v>227</v>
       </c>
       <c r="C206">
         <v>640</v>
@@ -15720,7 +16511,7 @@
         <v>205</v>
       </c>
       <c r="B207" t="s">
-        <v>73</v>
+        <v>228</v>
       </c>
       <c r="C207">
         <v>991</v>
@@ -15791,7 +16582,7 @@
         <v>206</v>
       </c>
       <c r="B208" t="s">
-        <v>84</v>
+        <v>229</v>
       </c>
       <c r="C208">
         <v>1172</v>
@@ -15862,7 +16653,7 @@
         <v>207</v>
       </c>
       <c r="B209" t="s">
-        <v>135</v>
+        <v>230</v>
       </c>
       <c r="C209">
         <v>691</v>
@@ -15933,7 +16724,7 @@
         <v>208</v>
       </c>
       <c r="B210" t="s">
-        <v>135</v>
+        <v>231</v>
       </c>
       <c r="C210">
         <v>683</v>
@@ -16004,7 +16795,7 @@
         <v>209</v>
       </c>
       <c r="B211" t="s">
-        <v>75</v>
+        <v>232</v>
       </c>
       <c r="C211">
         <v>607</v>
@@ -16075,7 +16866,7 @@
         <v>210</v>
       </c>
       <c r="B212" t="s">
-        <v>136</v>
+        <v>233</v>
       </c>
       <c r="C212">
         <v>1056</v>
@@ -16146,7 +16937,7 @@
         <v>211</v>
       </c>
       <c r="B213" t="s">
-        <v>137</v>
+        <v>234</v>
       </c>
       <c r="C213">
         <v>1180</v>
@@ -16217,7 +17008,7 @@
         <v>212</v>
       </c>
       <c r="B214" t="s">
-        <v>84</v>
+        <v>235</v>
       </c>
       <c r="C214">
         <v>1203</v>
@@ -16288,7 +17079,7 @@
         <v>213</v>
       </c>
       <c r="B215" t="s">
-        <v>138</v>
+        <v>236</v>
       </c>
       <c r="C215">
         <v>972</v>
@@ -16359,7 +17150,7 @@
         <v>214</v>
       </c>
       <c r="B216" t="s">
-        <v>84</v>
+        <v>237</v>
       </c>
       <c r="C216">
         <v>639</v>
@@ -16430,7 +17221,7 @@
         <v>215</v>
       </c>
       <c r="B217" t="s">
-        <v>37</v>
+        <v>238</v>
       </c>
       <c r="C217">
         <v>1115</v>
@@ -16501,7 +17292,7 @@
         <v>216</v>
       </c>
       <c r="B218" t="s">
-        <v>139</v>
+        <v>239</v>
       </c>
       <c r="C218">
         <v>998</v>
@@ -16572,7 +17363,7 @@
         <v>217</v>
       </c>
       <c r="B219" t="s">
-        <v>16</v>
+        <v>240</v>
       </c>
       <c r="C219">
         <v>880</v>
@@ -16643,7 +17434,7 @@
         <v>218</v>
       </c>
       <c r="B220" t="s">
-        <v>95</v>
+        <v>241</v>
       </c>
       <c r="C220">
         <v>905</v>
@@ -16714,7 +17505,7 @@
         <v>219</v>
       </c>
       <c r="B221" t="s">
-        <v>140</v>
+        <v>242</v>
       </c>
       <c r="C221">
         <v>1030</v>
@@ -16785,7 +17576,7 @@
         <v>220</v>
       </c>
       <c r="B222" t="s">
-        <v>139</v>
+        <v>243</v>
       </c>
       <c r="C222">
         <v>500</v>
@@ -16856,7 +17647,7 @@
         <v>221</v>
       </c>
       <c r="B223" t="s">
-        <v>54</v>
+        <v>244</v>
       </c>
       <c r="C223">
         <v>682</v>
@@ -16927,7 +17718,7 @@
         <v>222</v>
       </c>
       <c r="B224" t="s">
-        <v>56</v>
+        <v>245</v>
       </c>
       <c r="C224">
         <v>866</v>
@@ -16998,7 +17789,7 @@
         <v>223</v>
       </c>
       <c r="B225" t="s">
-        <v>64</v>
+        <v>246</v>
       </c>
       <c r="C225">
         <v>631</v>
@@ -17069,7 +17860,7 @@
         <v>224</v>
       </c>
       <c r="B226" t="s">
-        <v>65</v>
+        <v>247</v>
       </c>
       <c r="C226">
         <v>591</v>
@@ -17140,7 +17931,7 @@
         <v>225</v>
       </c>
       <c r="B227" t="s">
-        <v>141</v>
+        <v>248</v>
       </c>
       <c r="C227">
         <v>490</v>
@@ -17211,7 +18002,7 @@
         <v>226</v>
       </c>
       <c r="B228" t="s">
-        <v>142</v>
+        <v>249</v>
       </c>
       <c r="C228">
         <v>674</v>
@@ -17282,7 +18073,7 @@
         <v>227</v>
       </c>
       <c r="B229" t="s">
-        <v>143</v>
+        <v>250</v>
       </c>
       <c r="C229">
         <v>611</v>
@@ -17353,7 +18144,7 @@
         <v>228</v>
       </c>
       <c r="B230" t="s">
-        <v>54</v>
+        <v>251</v>
       </c>
       <c r="C230">
         <v>648</v>
@@ -17424,7 +18215,7 @@
         <v>229</v>
       </c>
       <c r="B231" t="s">
-        <v>56</v>
+        <v>252</v>
       </c>
       <c r="C231">
         <v>646</v>
@@ -17495,7 +18286,7 @@
         <v>230</v>
       </c>
       <c r="B232" t="s">
-        <v>52</v>
+        <v>253</v>
       </c>
       <c r="C232">
         <v>837</v>
@@ -17566,7 +18357,7 @@
         <v>231</v>
       </c>
       <c r="B233" t="s">
-        <v>86</v>
+        <v>254</v>
       </c>
       <c r="C233">
         <v>573</v>
@@ -17637,7 +18428,7 @@
         <v>232</v>
       </c>
       <c r="B234" t="s">
-        <v>144</v>
+        <v>255</v>
       </c>
       <c r="C234">
         <v>983</v>
@@ -17708,7 +18499,7 @@
         <v>233</v>
       </c>
       <c r="B235" t="s">
-        <v>3</v>
+        <v>256</v>
       </c>
       <c r="C235">
         <v>1074</v>
@@ -17779,7 +18570,7 @@
         <v>234</v>
       </c>
       <c r="B236" t="s">
-        <v>145</v>
+        <v>257</v>
       </c>
       <c r="C236">
         <v>496</v>
@@ -17850,7 +18641,7 @@
         <v>235</v>
       </c>
       <c r="B237" t="s">
-        <v>52</v>
+        <v>258</v>
       </c>
       <c r="C237">
         <v>968</v>
@@ -17921,7 +18712,7 @@
         <v>236</v>
       </c>
       <c r="B238" t="s">
-        <v>86</v>
+        <v>259</v>
       </c>
       <c r="C238">
         <v>1167</v>
@@ -17992,7 +18783,7 @@
         <v>237</v>
       </c>
       <c r="B239" t="s">
-        <v>52</v>
+        <v>260</v>
       </c>
       <c r="C239">
         <v>1053</v>
@@ -18063,7 +18854,7 @@
         <v>238</v>
       </c>
       <c r="B240" t="s">
-        <v>86</v>
+        <v>261</v>
       </c>
       <c r="C240">
         <v>1066</v>
@@ -18134,7 +18925,7 @@
         <v>239</v>
       </c>
       <c r="B241" t="s">
-        <v>146</v>
+        <v>262</v>
       </c>
       <c r="C241">
         <v>830</v>
@@ -18205,7 +18996,7 @@
         <v>240</v>
       </c>
       <c r="B242" t="s">
-        <v>147</v>
+        <v>263</v>
       </c>
       <c r="C242">
         <v>529</v>
@@ -18276,7 +19067,7 @@
         <v>241</v>
       </c>
       <c r="B243" t="s">
-        <v>3</v>
+        <v>264</v>
       </c>
       <c r="C243">
         <v>705</v>
@@ -18347,7 +19138,7 @@
         <v>242</v>
       </c>
       <c r="B244" t="s">
-        <v>148</v>
+        <v>265</v>
       </c>
       <c r="C244">
         <v>432</v>
@@ -18418,7 +19209,7 @@
         <v>243</v>
       </c>
       <c r="B245" t="s">
-        <v>149</v>
+        <v>266</v>
       </c>
       <c r="C245">
         <v>1043</v>
@@ -18489,7 +19280,7 @@
         <v>244</v>
       </c>
       <c r="B246" t="s">
-        <v>59</v>
+        <v>267</v>
       </c>
       <c r="C246">
         <v>545</v>
@@ -18560,7 +19351,7 @@
         <v>245</v>
       </c>
       <c r="B247" t="s">
-        <v>150</v>
+        <v>268</v>
       </c>
       <c r="C247">
         <v>832</v>
@@ -18631,7 +19422,7 @@
         <v>246</v>
       </c>
       <c r="B248" t="s">
-        <v>52</v>
+        <v>269</v>
       </c>
       <c r="C248">
         <v>673</v>
@@ -18702,7 +19493,7 @@
         <v>247</v>
       </c>
       <c r="B249" t="s">
-        <v>86</v>
+        <v>270</v>
       </c>
       <c r="C249">
         <v>745</v>
@@ -18773,7 +19564,7 @@
         <v>248</v>
       </c>
       <c r="B250" t="s">
-        <v>64</v>
+        <v>271</v>
       </c>
       <c r="C250">
         <v>876</v>
@@ -18844,7 +19635,7 @@
         <v>249</v>
       </c>
       <c r="B251" t="s">
-        <v>65</v>
+        <v>272</v>
       </c>
       <c r="C251">
         <v>566</v>
@@ -18915,7 +19706,7 @@
         <v>250</v>
       </c>
       <c r="B252" t="s">
-        <v>3</v>
+        <v>273</v>
       </c>
       <c r="C252">
         <v>1166</v>
@@ -18986,7 +19777,7 @@
         <v>251</v>
       </c>
       <c r="B253" t="s">
-        <v>151</v>
+        <v>274</v>
       </c>
       <c r="C253">
         <v>949</v>
@@ -19057,7 +19848,7 @@
         <v>252</v>
       </c>
       <c r="B254" t="s">
-        <v>152</v>
+        <v>275</v>
       </c>
       <c r="C254">
         <v>952</v>
@@ -19128,7 +19919,7 @@
         <v>253</v>
       </c>
       <c r="B255" t="s">
-        <v>153</v>
+        <v>276</v>
       </c>
       <c r="C255">
         <v>878</v>
@@ -19199,7 +19990,7 @@
         <v>254</v>
       </c>
       <c r="B256" t="s">
-        <v>3</v>
+        <v>277</v>
       </c>
       <c r="C256">
         <v>776</v>
@@ -19270,7 +20061,7 @@
         <v>255</v>
       </c>
       <c r="B257" t="s">
-        <v>153</v>
+        <v>278</v>
       </c>
       <c r="C257">
         <v>686</v>
@@ -19341,7 +20132,7 @@
         <v>256</v>
       </c>
       <c r="B258" t="s">
-        <v>154</v>
+        <v>279</v>
       </c>
       <c r="C258">
         <v>1193</v>
@@ -19412,7 +20203,7 @@
         <v>257</v>
       </c>
       <c r="B259" t="s">
-        <v>155</v>
+        <v>280</v>
       </c>
       <c r="C259">
         <v>1043</v>
@@ -19483,7 +20274,7 @@
         <v>258</v>
       </c>
       <c r="B260" t="s">
-        <v>16</v>
+        <v>281</v>
       </c>
       <c r="C260">
         <v>965</v>
@@ -19554,7 +20345,7 @@
         <v>259</v>
       </c>
       <c r="B261" t="s">
-        <v>156</v>
+        <v>282</v>
       </c>
       <c r="C261">
         <v>1017</v>
@@ -19625,7 +20416,7 @@
         <v>260</v>
       </c>
       <c r="B262" t="s">
-        <v>157</v>
+        <v>283</v>
       </c>
       <c r="C262">
         <v>1026</v>
@@ -19696,7 +20487,7 @@
         <v>261</v>
       </c>
       <c r="B263" t="s">
-        <v>158</v>
+        <v>284</v>
       </c>
       <c r="C263">
         <v>1041</v>
@@ -19767,7 +20558,7 @@
         <v>262</v>
       </c>
       <c r="B264" t="s">
-        <v>159</v>
+        <v>285</v>
       </c>
       <c r="C264">
         <v>1176</v>
@@ -19838,7 +20629,7 @@
         <v>263</v>
       </c>
       <c r="B265" t="s">
-        <v>160</v>
+        <v>286</v>
       </c>
       <c r="C265">
         <v>633</v>
@@ -19909,7 +20700,7 @@
         <v>264</v>
       </c>
       <c r="B266" t="s">
-        <v>161</v>
+        <v>287</v>
       </c>
       <c r="C266">
         <v>618</v>
@@ -19980,7 +20771,7 @@
         <v>265</v>
       </c>
       <c r="B267" t="s">
-        <v>162</v>
+        <v>288</v>
       </c>
       <c r="C267">
         <v>974</v>
@@ -20051,7 +20842,7 @@
         <v>266</v>
       </c>
       <c r="B268" t="s">
-        <v>163</v>
+        <v>289</v>
       </c>
       <c r="C268">
         <v>992</v>
@@ -20122,7 +20913,7 @@
         <v>267</v>
       </c>
       <c r="B269" t="s">
-        <v>164</v>
+        <v>290</v>
       </c>
       <c r="C269">
         <v>790</v>
@@ -20193,7 +20984,7 @@
         <v>268</v>
       </c>
       <c r="B270" t="s">
-        <v>136</v>
+        <v>291</v>
       </c>
       <c r="C270">
         <v>1070</v>
@@ -20264,7 +21055,7 @@
         <v>269</v>
       </c>
       <c r="B271" t="s">
-        <v>137</v>
+        <v>292</v>
       </c>
       <c r="C271">
         <v>413</v>
@@ -20335,7 +21126,7 @@
         <v>270</v>
       </c>
       <c r="B272" t="s">
-        <v>143</v>
+        <v>293</v>
       </c>
       <c r="C272">
         <v>726</v>
@@ -20406,7 +21197,7 @@
         <v>271</v>
       </c>
       <c r="B273" t="s">
-        <v>59</v>
+        <v>294</v>
       </c>
       <c r="C273">
         <v>623</v>
@@ -20477,7 +21268,7 @@
         <v>272</v>
       </c>
       <c r="B274" t="s">
-        <v>75</v>
+        <v>295</v>
       </c>
       <c r="C274">
         <v>1043</v>
@@ -20548,7 +21339,7 @@
         <v>273</v>
       </c>
       <c r="B275" t="s">
-        <v>54</v>
+        <v>296</v>
       </c>
       <c r="C275">
         <v>700</v>
@@ -20619,7 +21410,7 @@
         <v>274</v>
       </c>
       <c r="B276" t="s">
-        <v>56</v>
+        <v>297</v>
       </c>
       <c r="C276">
         <v>633</v>
@@ -20690,7 +21481,7 @@
         <v>275</v>
       </c>
       <c r="B277" t="s">
-        <v>52</v>
+        <v>298</v>
       </c>
       <c r="C277">
         <v>759</v>
@@ -20761,7 +21552,7 @@
         <v>276</v>
       </c>
       <c r="B278" t="s">
-        <v>86</v>
+        <v>299</v>
       </c>
       <c r="C278">
         <v>733</v>
@@ -20832,7 +21623,7 @@
         <v>277</v>
       </c>
       <c r="B279" t="s">
-        <v>165</v>
+        <v>300</v>
       </c>
       <c r="C279">
         <v>780</v>
@@ -20903,7 +21694,7 @@
         <v>278</v>
       </c>
       <c r="B280" t="s">
-        <v>166</v>
+        <v>301</v>
       </c>
       <c r="C280">
         <v>662</v>
@@ -20974,7 +21765,7 @@
         <v>279</v>
       </c>
       <c r="B281" t="s">
-        <v>50</v>
+        <v>302</v>
       </c>
       <c r="C281">
         <v>914</v>
@@ -21045,7 +21836,7 @@
         <v>280</v>
       </c>
       <c r="B282" t="s">
-        <v>52</v>
+        <v>303</v>
       </c>
       <c r="C282">
         <v>656</v>
@@ -21116,7 +21907,7 @@
         <v>281</v>
       </c>
       <c r="B283" t="s">
-        <v>86</v>
+        <v>304</v>
       </c>
       <c r="C283">
         <v>640</v>
@@ -21187,7 +21978,7 @@
         <v>282</v>
       </c>
       <c r="B284" t="s">
-        <v>75</v>
+        <v>305</v>
       </c>
       <c r="C284">
         <v>703</v>
@@ -21258,7 +22049,7 @@
         <v>283</v>
       </c>
       <c r="B285" t="s">
-        <v>166</v>
+        <v>306</v>
       </c>
       <c r="C285">
         <v>831</v>
@@ -21329,7 +22120,7 @@
         <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>153</v>
+        <v>307</v>
       </c>
       <c r="C286">
         <v>986</v>
@@ -21400,7 +22191,7 @@
         <v>285</v>
       </c>
       <c r="B287" t="s">
-        <v>167</v>
+        <v>308</v>
       </c>
       <c r="C287">
         <v>684</v>
@@ -21471,7 +22262,7 @@
         <v>286</v>
       </c>
       <c r="B288" t="s">
-        <v>168</v>
+        <v>129</v>
       </c>
       <c r="C288">
         <v>692</v>
@@ -21542,7 +22333,7 @@
         <v>287</v>
       </c>
       <c r="B289" t="s">
-        <v>6</v>
+        <v>309</v>
       </c>
       <c r="C289">
         <v>903</v>
@@ -21613,7 +22404,7 @@
         <v>288</v>
       </c>
       <c r="B290" t="s">
-        <v>7</v>
+        <v>310</v>
       </c>
       <c r="C290">
         <v>713</v>
@@ -21684,7 +22475,7 @@
         <v>289</v>
       </c>
       <c r="B291" t="s">
-        <v>169</v>
+        <v>311</v>
       </c>
       <c r="C291">
         <v>1118</v>
@@ -21755,7 +22546,7 @@
         <v>290</v>
       </c>
       <c r="B292" t="s">
-        <v>170</v>
+        <v>312</v>
       </c>
       <c r="C292">
         <v>1167</v>
@@ -21826,7 +22617,7 @@
         <v>291</v>
       </c>
       <c r="B293" t="s">
-        <v>171</v>
+        <v>38</v>
       </c>
       <c r="C293">
         <v>1013</v>
@@ -21897,7 +22688,7 @@
         <v>292</v>
       </c>
       <c r="B294" t="s">
-        <v>172</v>
+        <v>313</v>
       </c>
       <c r="C294">
         <v>1148</v>
@@ -21968,7 +22759,7 @@
         <v>293</v>
       </c>
       <c r="B295" t="s">
-        <v>173</v>
+        <v>314</v>
       </c>
       <c r="C295">
         <v>1011</v>
@@ -22039,7 +22830,7 @@
         <v>294</v>
       </c>
       <c r="B296" t="s">
-        <v>174</v>
+        <v>315</v>
       </c>
       <c r="C296">
         <v>893</v>
@@ -22110,7 +22901,7 @@
         <v>295</v>
       </c>
       <c r="B297" t="s">
-        <v>175</v>
+        <v>316</v>
       </c>
       <c r="C297">
         <v>1024</v>
@@ -22181,7 +22972,7 @@
         <v>296</v>
       </c>
       <c r="B298" t="s">
-        <v>176</v>
+        <v>317</v>
       </c>
       <c r="C298">
         <v>673</v>
@@ -22252,7 +23043,7 @@
         <v>297</v>
       </c>
       <c r="B299" t="s">
-        <v>177</v>
+        <v>318</v>
       </c>
       <c r="C299">
         <v>914</v>
@@ -22323,7 +23114,7 @@
         <v>298</v>
       </c>
       <c r="B300" t="s">
-        <v>178</v>
+        <v>319</v>
       </c>
       <c r="C300">
         <v>852</v>
@@ -22394,7 +23185,7 @@
         <v>299</v>
       </c>
       <c r="B301" t="s">
-        <v>179</v>
+        <v>320</v>
       </c>
       <c r="C301">
         <v>1119</v>
@@ -22465,7 +23256,7 @@
         <v>300</v>
       </c>
       <c r="B302" t="s">
-        <v>180</v>
+        <v>321</v>
       </c>
       <c r="C302">
         <v>955</v>
@@ -22536,7 +23327,7 @@
         <v>301</v>
       </c>
       <c r="B303" t="s">
-        <v>181</v>
+        <v>322</v>
       </c>
       <c r="C303">
         <v>779</v>
@@ -22607,7 +23398,7 @@
         <v>302</v>
       </c>
       <c r="B304" t="s">
-        <v>182</v>
+        <v>323</v>
       </c>
       <c r="C304">
         <v>1092</v>
@@ -22678,7 +23469,7 @@
         <v>303</v>
       </c>
       <c r="B305" t="s">
-        <v>183</v>
+        <v>324</v>
       </c>
       <c r="C305">
         <v>835</v>
@@ -22749,7 +23540,7 @@
         <v>304</v>
       </c>
       <c r="B306" t="s">
-        <v>184</v>
+        <v>325</v>
       </c>
       <c r="C306">
         <v>577</v>
@@ -22820,7 +23611,7 @@
         <v>305</v>
       </c>
       <c r="B307" t="s">
-        <v>185</v>
+        <v>326</v>
       </c>
       <c r="C307">
         <v>1022</v>
@@ -22891,7 +23682,7 @@
         <v>306</v>
       </c>
       <c r="B308" t="s">
-        <v>186</v>
+        <v>327</v>
       </c>
       <c r="C308">
         <v>1000</v>
@@ -22962,7 +23753,7 @@
         <v>307</v>
       </c>
       <c r="B309" t="s">
-        <v>187</v>
+        <v>328</v>
       </c>
       <c r="C309">
         <v>1058</v>
@@ -23033,7 +23824,7 @@
         <v>308</v>
       </c>
       <c r="B310" t="s">
-        <v>146</v>
+        <v>329</v>
       </c>
       <c r="C310">
         <v>841</v>
@@ -23104,7 +23895,7 @@
         <v>309</v>
       </c>
       <c r="B311" t="s">
-        <v>147</v>
+        <v>330</v>
       </c>
       <c r="C311">
         <v>734</v>
@@ -23175,7 +23966,7 @@
         <v>310</v>
       </c>
       <c r="B312" t="s">
-        <v>188</v>
+        <v>331</v>
       </c>
       <c r="C312">
         <v>637</v>
@@ -23246,7 +24037,7 @@
         <v>311</v>
       </c>
       <c r="B313" t="s">
-        <v>189</v>
+        <v>332</v>
       </c>
       <c r="C313">
         <v>632</v>
@@ -23317,7 +24108,7 @@
         <v>312</v>
       </c>
       <c r="B314" t="s">
-        <v>190</v>
+        <v>333</v>
       </c>
       <c r="C314">
         <v>668</v>
@@ -23388,7 +24179,7 @@
         <v>313</v>
       </c>
       <c r="B315" t="s">
-        <v>191</v>
+        <v>334</v>
       </c>
       <c r="C315">
         <v>658</v>
@@ -23459,7 +24250,7 @@
         <v>314</v>
       </c>
       <c r="B316" t="s">
-        <v>192</v>
+        <v>335</v>
       </c>
       <c r="C316">
         <v>627</v>
@@ -23530,7 +24321,7 @@
         <v>315</v>
       </c>
       <c r="B317" t="s">
-        <v>193</v>
+        <v>336</v>
       </c>
       <c r="C317">
         <v>644</v>
@@ -23601,7 +24392,7 @@
         <v>316</v>
       </c>
       <c r="B318" t="s">
-        <v>148</v>
+        <v>337</v>
       </c>
       <c r="C318">
         <v>795</v>
@@ -23672,7 +24463,7 @@
         <v>317</v>
       </c>
       <c r="B319" t="s">
-        <v>87</v>
+        <v>338</v>
       </c>
       <c r="C319">
         <v>804</v>
@@ -23743,7 +24534,7 @@
         <v>318</v>
       </c>
       <c r="B320" t="s">
-        <v>88</v>
+        <v>339</v>
       </c>
       <c r="C320">
         <v>827</v>
@@ -23814,7 +24605,7 @@
         <v>319</v>
       </c>
       <c r="B321" t="s">
-        <v>194</v>
+        <v>340</v>
       </c>
       <c r="C321">
         <v>1094</v>
@@ -23885,7 +24676,7 @@
         <v>320</v>
       </c>
       <c r="B322" t="s">
-        <v>133</v>
+        <v>341</v>
       </c>
       <c r="C322">
         <v>1132</v>
@@ -23956,7 +24747,7 @@
         <v>321</v>
       </c>
       <c r="B323" t="s">
-        <v>134</v>
+        <v>342</v>
       </c>
       <c r="C323">
         <v>947</v>
@@ -24027,7 +24818,7 @@
         <v>322</v>
       </c>
       <c r="B324" t="s">
-        <v>52</v>
+        <v>343</v>
       </c>
       <c r="C324">
         <v>647</v>
@@ -24098,7 +24889,7 @@
         <v>323</v>
       </c>
       <c r="B325" t="s">
-        <v>86</v>
+        <v>344</v>
       </c>
       <c r="C325">
         <v>644</v>
@@ -24169,7 +24960,7 @@
         <v>324</v>
       </c>
       <c r="B326" t="s">
-        <v>146</v>
+        <v>345</v>
       </c>
       <c r="C326">
         <v>779</v>
@@ -24240,7 +25031,7 @@
         <v>325</v>
       </c>
       <c r="B327" t="s">
-        <v>147</v>
+        <v>346</v>
       </c>
       <c r="C327">
         <v>496</v>
@@ -24311,7 +25102,7 @@
         <v>326</v>
       </c>
       <c r="B328" t="s">
-        <v>50</v>
+        <v>347</v>
       </c>
       <c r="C328">
         <v>864</v>
@@ -24382,7 +25173,7 @@
         <v>327</v>
       </c>
       <c r="B329" t="s">
-        <v>141</v>
+        <v>348</v>
       </c>
       <c r="C329">
         <v>502</v>
@@ -24453,7 +25244,7 @@
         <v>328</v>
       </c>
       <c r="B330" t="s">
-        <v>51</v>
+        <v>316</v>
       </c>
       <c r="C330">
         <v>472</v>
@@ -24524,7 +25315,7 @@
         <v>329</v>
       </c>
       <c r="B331" t="s">
-        <v>3</v>
+        <v>349</v>
       </c>
       <c r="C331">
         <v>1075</v>
@@ -24595,7 +25386,7 @@
         <v>330</v>
       </c>
       <c r="B332" t="s">
-        <v>75</v>
+        <v>350</v>
       </c>
       <c r="C332">
         <v>942</v>
@@ -24666,7 +25457,7 @@
         <v>331</v>
       </c>
       <c r="B333" t="s">
-        <v>52</v>
+        <v>351</v>
       </c>
       <c r="C333">
         <v>759</v>
@@ -24737,7 +25528,7 @@
         <v>332</v>
       </c>
       <c r="B334" t="s">
-        <v>86</v>
+        <v>352</v>
       </c>
       <c r="C334">
         <v>920</v>
@@ -24808,7 +25599,7 @@
         <v>333</v>
       </c>
       <c r="B335" t="s">
-        <v>195</v>
+        <v>353</v>
       </c>
       <c r="C335">
         <v>650</v>
@@ -24879,7 +25670,7 @@
         <v>334</v>
       </c>
       <c r="B336" t="s">
-        <v>196</v>
+        <v>354</v>
       </c>
       <c r="C336">
         <v>607</v>
@@ -24950,7 +25741,7 @@
         <v>335</v>
       </c>
       <c r="B337" t="s">
-        <v>197</v>
+        <v>355</v>
       </c>
       <c r="C337">
         <v>731</v>
@@ -25021,7 +25812,7 @@
         <v>336</v>
       </c>
       <c r="B338" t="s">
-        <v>198</v>
+        <v>356</v>
       </c>
       <c r="C338">
         <v>1132</v>
@@ -25092,7 +25883,7 @@
         <v>337</v>
       </c>
       <c r="B339" t="s">
-        <v>199</v>
+        <v>357</v>
       </c>
       <c r="C339">
         <v>399</v>
@@ -25163,7 +25954,7 @@
         <v>338</v>
       </c>
       <c r="B340" t="s">
-        <v>153</v>
+        <v>358</v>
       </c>
       <c r="C340">
         <v>567</v>
@@ -25234,7 +26025,7 @@
         <v>339</v>
       </c>
       <c r="B341" t="s">
-        <v>200</v>
+        <v>359</v>
       </c>
       <c r="C341">
         <v>787</v>
@@ -25305,7 +26096,7 @@
         <v>340</v>
       </c>
       <c r="B342" t="s">
-        <v>201</v>
+        <v>360</v>
       </c>
       <c r="C342">
         <v>961</v>
@@ -25376,7 +26167,7 @@
         <v>341</v>
       </c>
       <c r="B343" t="s">
-        <v>202</v>
+        <v>361</v>
       </c>
       <c r="C343">
         <v>1062</v>
@@ -25447,7 +26238,7 @@
         <v>342</v>
       </c>
       <c r="B344" t="s">
-        <v>203</v>
+        <v>362</v>
       </c>
       <c r="C344">
         <v>1008</v>
@@ -25518,7 +26309,7 @@
         <v>343</v>
       </c>
       <c r="B345" t="s">
-        <v>204</v>
+        <v>363</v>
       </c>
       <c r="C345">
         <v>678</v>
@@ -25589,7 +26380,7 @@
         <v>344</v>
       </c>
       <c r="B346" t="s">
-        <v>205</v>
+        <v>364</v>
       </c>
       <c r="C346">
         <v>940</v>
@@ -25660,7 +26451,7 @@
         <v>345</v>
       </c>
       <c r="B347" t="s">
-        <v>206</v>
+        <v>365</v>
       </c>
       <c r="C347">
         <v>810</v>
@@ -25731,7 +26522,7 @@
         <v>346</v>
       </c>
       <c r="B348" t="s">
-        <v>207</v>
+        <v>366</v>
       </c>
       <c r="C348">
         <v>953</v>
@@ -25802,7 +26593,7 @@
         <v>347</v>
       </c>
       <c r="B349" t="s">
-        <v>205</v>
+        <v>367</v>
       </c>
       <c r="C349">
         <v>836</v>
@@ -25873,7 +26664,7 @@
         <v>348</v>
       </c>
       <c r="B350" t="s">
-        <v>208</v>
+        <v>368</v>
       </c>
       <c r="C350">
         <v>1141</v>
@@ -25944,7 +26735,7 @@
         <v>349</v>
       </c>
       <c r="B351" t="s">
-        <v>103</v>
+        <v>369</v>
       </c>
       <c r="C351">
         <v>1136</v>
@@ -26015,7 +26806,7 @@
         <v>350</v>
       </c>
       <c r="B352" t="s">
-        <v>209</v>
+        <v>370</v>
       </c>
       <c r="C352">
         <v>1077</v>
@@ -26086,7 +26877,7 @@
         <v>351</v>
       </c>
       <c r="B353" t="s">
-        <v>210</v>
+        <v>371</v>
       </c>
       <c r="C353">
         <v>1104</v>
@@ -26157,7 +26948,7 @@
         <v>352</v>
       </c>
       <c r="B354" t="s">
-        <v>211</v>
+        <v>372</v>
       </c>
       <c r="C354">
         <v>643</v>
@@ -26228,7 +27019,7 @@
         <v>353</v>
       </c>
       <c r="B355" t="s">
-        <v>212</v>
+        <v>373</v>
       </c>
       <c r="C355">
         <v>645</v>
@@ -26299,7 +27090,7 @@
         <v>354</v>
       </c>
       <c r="B356" t="s">
-        <v>52</v>
+        <v>374</v>
       </c>
       <c r="C356">
         <v>469</v>
@@ -26370,7 +27161,7 @@
         <v>355</v>
       </c>
       <c r="B357" t="s">
-        <v>86</v>
+        <v>375</v>
       </c>
       <c r="C357">
         <v>737</v>
@@ -26441,7 +27232,7 @@
         <v>356</v>
       </c>
       <c r="B358" t="s">
-        <v>213</v>
+        <v>376</v>
       </c>
       <c r="C358">
         <v>833</v>
@@ -26512,7 +27303,7 @@
         <v>357</v>
       </c>
       <c r="B359" t="s">
-        <v>214</v>
+        <v>377</v>
       </c>
       <c r="C359">
         <v>806</v>
@@ -26583,7 +27374,7 @@
         <v>358</v>
       </c>
       <c r="B360" t="s">
-        <v>119</v>
+        <v>378</v>
       </c>
       <c r="C360">
         <v>976</v>
@@ -26654,7 +27445,7 @@
         <v>359</v>
       </c>
       <c r="B361" t="s">
-        <v>120</v>
+        <v>379</v>
       </c>
       <c r="C361">
         <v>640</v>
@@ -26725,7 +27516,7 @@
         <v>360</v>
       </c>
       <c r="B362" t="s">
-        <v>215</v>
+        <v>380</v>
       </c>
       <c r="C362">
         <v>565</v>
@@ -26796,7 +27587,7 @@
         <v>361</v>
       </c>
       <c r="B363" t="s">
-        <v>216</v>
+        <v>381</v>
       </c>
       <c r="C363">
         <v>1181</v>
@@ -26867,7 +27658,7 @@
         <v>362</v>
       </c>
       <c r="B364" t="s">
-        <v>54</v>
+        <v>382</v>
       </c>
       <c r="C364">
         <v>1145</v>
@@ -26938,7 +27729,7 @@
         <v>363</v>
       </c>
       <c r="B365" t="s">
-        <v>56</v>
+        <v>383</v>
       </c>
       <c r="C365">
         <v>571</v>
@@ -27009,7 +27800,7 @@
         <v>364</v>
       </c>
       <c r="B366" t="s">
-        <v>95</v>
+        <v>384</v>
       </c>
       <c r="C366">
         <v>930</v>
@@ -27080,7 +27871,7 @@
         <v>365</v>
       </c>
       <c r="B367" t="s">
-        <v>217</v>
+        <v>385</v>
       </c>
       <c r="C367">
         <v>633</v>
@@ -27151,7 +27942,7 @@
         <v>366</v>
       </c>
       <c r="B368" t="s">
-        <v>218</v>
+        <v>386</v>
       </c>
       <c r="C368">
         <v>764</v>
@@ -27222,7 +28013,7 @@
         <v>367</v>
       </c>
       <c r="B369" t="s">
-        <v>219</v>
+        <v>387</v>
       </c>
       <c r="C369">
         <v>972</v>
@@ -27293,7 +28084,7 @@
         <v>368</v>
       </c>
       <c r="B370" t="s">
-        <v>220</v>
+        <v>388</v>
       </c>
       <c r="C370">
         <v>1116</v>
@@ -27364,7 +28155,7 @@
         <v>369</v>
       </c>
       <c r="B371" t="s">
-        <v>80</v>
+        <v>389</v>
       </c>
       <c r="C371">
         <v>660</v>
@@ -27435,7 +28226,7 @@
         <v>370</v>
       </c>
       <c r="B372" t="s">
-        <v>81</v>
+        <v>390</v>
       </c>
       <c r="C372">
         <v>771</v>
@@ -27506,7 +28297,7 @@
         <v>371</v>
       </c>
       <c r="B373" t="s">
-        <v>51</v>
+        <v>391</v>
       </c>
       <c r="C373">
         <v>692</v>
@@ -27577,7 +28368,7 @@
         <v>372</v>
       </c>
       <c r="B374" t="s">
-        <v>103</v>
+        <v>392</v>
       </c>
       <c r="C374">
         <v>992</v>
@@ -27648,7 +28439,7 @@
         <v>373</v>
       </c>
       <c r="B375" t="s">
-        <v>122</v>
+        <v>393</v>
       </c>
       <c r="C375">
         <v>903</v>
@@ -27719,7 +28510,7 @@
         <v>374</v>
       </c>
       <c r="B376" t="s">
-        <v>121</v>
+        <v>394</v>
       </c>
       <c r="C376">
         <v>540</v>
@@ -27790,7 +28581,7 @@
         <v>375</v>
       </c>
       <c r="B377" t="s">
-        <v>121</v>
+        <v>395</v>
       </c>
       <c r="C377">
         <v>1202</v>
@@ -27861,7 +28652,7 @@
         <v>376</v>
       </c>
       <c r="B378" t="s">
-        <v>221</v>
+        <v>396</v>
       </c>
       <c r="C378">
         <v>640</v>
@@ -27932,7 +28723,7 @@
         <v>377</v>
       </c>
       <c r="B379" t="s">
-        <v>166</v>
+        <v>397</v>
       </c>
       <c r="C379">
         <v>1108</v>
@@ -28003,7 +28794,7 @@
         <v>378</v>
       </c>
       <c r="B380" t="s">
-        <v>166</v>
+        <v>398</v>
       </c>
       <c r="C380">
         <v>979</v>
@@ -28074,7 +28865,7 @@
         <v>379</v>
       </c>
       <c r="B381" t="s">
-        <v>222</v>
+        <v>399</v>
       </c>
       <c r="C381">
         <v>944</v>
@@ -28145,7 +28936,7 @@
         <v>380</v>
       </c>
       <c r="B382" t="s">
-        <v>223</v>
+        <v>400</v>
       </c>
       <c r="C382">
         <v>1018</v>
@@ -28216,7 +29007,7 @@
         <v>381</v>
       </c>
       <c r="B383" t="s">
-        <v>224</v>
+        <v>401</v>
       </c>
       <c r="C383">
         <v>797</v>
@@ -28287,7 +29078,7 @@
         <v>382</v>
       </c>
       <c r="B384" t="s">
-        <v>225</v>
+        <v>402</v>
       </c>
       <c r="C384">
         <v>1097</v>
@@ -28358,7 +29149,7 @@
         <v>383</v>
       </c>
       <c r="B385" t="s">
-        <v>226</v>
+        <v>403</v>
       </c>
       <c r="C385">
         <v>559</v>
@@ -28429,7 +29220,7 @@
         <v>384</v>
       </c>
       <c r="B386" t="s">
-        <v>227</v>
+        <v>404</v>
       </c>
       <c r="C386">
         <v>502</v>
@@ -28500,7 +29291,7 @@
         <v>385</v>
       </c>
       <c r="B387" t="s">
-        <v>228</v>
+        <v>405</v>
       </c>
       <c r="C387">
         <v>754</v>
@@ -28571,7 +29362,7 @@
         <v>386</v>
       </c>
       <c r="B388" t="s">
-        <v>84</v>
+        <v>406</v>
       </c>
       <c r="C388">
         <v>558</v>
@@ -28642,7 +29433,7 @@
         <v>387</v>
       </c>
       <c r="B389" t="s">
-        <v>229</v>
+        <v>407</v>
       </c>
       <c r="C389">
         <v>710</v>
@@ -28713,7 +29504,7 @@
         <v>388</v>
       </c>
       <c r="B390" t="s">
-        <v>103</v>
+        <v>408</v>
       </c>
       <c r="C390">
         <v>887</v>
@@ -28784,7 +29575,7 @@
         <v>389</v>
       </c>
       <c r="B391" t="s">
-        <v>103</v>
+        <v>409</v>
       </c>
       <c r="C391">
         <v>630</v>
@@ -28855,7 +29646,7 @@
         <v>390</v>
       </c>
       <c r="B392" t="s">
-        <v>215</v>
+        <v>410</v>
       </c>
       <c r="C392">
         <v>777</v>
@@ -28926,7 +29717,7 @@
         <v>391</v>
       </c>
       <c r="B393" t="s">
-        <v>216</v>
+        <v>411</v>
       </c>
       <c r="C393">
         <v>765</v>
@@ -28997,7 +29788,7 @@
         <v>392</v>
       </c>
       <c r="B394" t="s">
-        <v>103</v>
+        <v>412</v>
       </c>
       <c r="C394">
         <v>1138</v>
@@ -29068,7 +29859,7 @@
         <v>393</v>
       </c>
       <c r="B395" t="s">
-        <v>121</v>
+        <v>413</v>
       </c>
       <c r="C395">
         <v>405</v>
@@ -29139,7 +29930,7 @@
         <v>394</v>
       </c>
       <c r="B396" t="s">
-        <v>52</v>
+        <v>414</v>
       </c>
       <c r="C396">
         <v>653</v>
@@ -29210,7 +30001,7 @@
         <v>395</v>
       </c>
       <c r="B397" t="s">
-        <v>86</v>
+        <v>415</v>
       </c>
       <c r="C397">
         <v>625</v>
@@ -29281,7 +30072,7 @@
         <v>396</v>
       </c>
       <c r="B398" t="s">
-        <v>97</v>
+        <v>416</v>
       </c>
       <c r="C398">
         <v>629</v>
@@ -29352,7 +30143,7 @@
         <v>397</v>
       </c>
       <c r="B399" t="s">
-        <v>98</v>
+        <v>417</v>
       </c>
       <c r="C399">
         <v>626</v>
@@ -29423,7 +30214,7 @@
         <v>398</v>
       </c>
       <c r="B400" t="s">
-        <v>122</v>
+        <v>418</v>
       </c>
       <c r="C400">
         <v>499</v>
@@ -29494,7 +30285,7 @@
         <v>399</v>
       </c>
       <c r="B401" t="s">
-        <v>123</v>
+        <v>419</v>
       </c>
       <c r="C401">
         <v>329</v>
@@ -29565,7 +30356,7 @@
         <v>400</v>
       </c>
       <c r="B402" t="s">
-        <v>73</v>
+        <v>420</v>
       </c>
       <c r="C402">
         <v>681</v>
@@ -29636,7 +30427,7 @@
         <v>401</v>
       </c>
       <c r="B403" t="s">
-        <v>230</v>
+        <v>421</v>
       </c>
       <c r="C403">
         <v>950</v>
@@ -29707,7 +30498,7 @@
         <v>402</v>
       </c>
       <c r="B404" t="s">
-        <v>108</v>
+        <v>422</v>
       </c>
       <c r="C404">
         <v>805</v>
@@ -29778,7 +30569,7 @@
         <v>403</v>
       </c>
       <c r="B405" t="s">
-        <v>109</v>
+        <v>423</v>
       </c>
       <c r="C405">
         <v>824</v>
@@ -29849,7 +30640,7 @@
         <v>404</v>
       </c>
       <c r="B406" t="s">
-        <v>231</v>
+        <v>424</v>
       </c>
       <c r="C406">
         <v>795</v>
@@ -29920,7 +30711,7 @@
         <v>405</v>
       </c>
       <c r="B407" t="s">
-        <v>73</v>
+        <v>425</v>
       </c>
       <c r="C407">
         <v>984</v>
@@ -29991,7 +30782,7 @@
         <v>406</v>
       </c>
       <c r="B408" t="s">
-        <v>111</v>
+        <v>426</v>
       </c>
       <c r="C408">
         <v>798</v>
@@ -30062,7 +30853,7 @@
         <v>407</v>
       </c>
       <c r="B409" t="s">
-        <v>232</v>
+        <v>427</v>
       </c>
       <c r="C409">
         <v>1065</v>
@@ -30133,7 +30924,7 @@
         <v>408</v>
       </c>
       <c r="B410" t="s">
-        <v>233</v>
+        <v>428</v>
       </c>
       <c r="C410">
         <v>651</v>
@@ -30204,7 +30995,7 @@
         <v>409</v>
       </c>
       <c r="B411" t="s">
-        <v>234</v>
+        <v>429</v>
       </c>
       <c r="C411">
         <v>666</v>
@@ -30275,7 +31066,7 @@
         <v>410</v>
       </c>
       <c r="B412" t="s">
-        <v>103</v>
+        <v>430</v>
       </c>
       <c r="C412">
         <v>695</v>
@@ -30346,7 +31137,7 @@
         <v>411</v>
       </c>
       <c r="B413" t="s">
-        <v>104</v>
+        <v>431</v>
       </c>
       <c r="C413">
         <v>561</v>
@@ -30417,7 +31208,7 @@
         <v>412</v>
       </c>
       <c r="B414" t="s">
-        <v>84</v>
+        <v>432</v>
       </c>
       <c r="C414">
         <v>528</v>
@@ -30488,7 +31279,7 @@
         <v>413</v>
       </c>
       <c r="B415" t="s">
-        <v>226</v>
+        <v>433</v>
       </c>
       <c r="C415">
         <v>374</v>
@@ -30559,7 +31350,7 @@
         <v>414</v>
       </c>
       <c r="B416" t="s">
-        <v>45</v>
+        <v>434</v>
       </c>
       <c r="C416">
         <v>544</v>
@@ -30630,7 +31421,7 @@
         <v>415</v>
       </c>
       <c r="B417" t="s">
-        <v>9</v>
+        <v>435</v>
       </c>
       <c r="C417">
         <v>473</v>
@@ -30701,7 +31492,7 @@
         <v>416</v>
       </c>
       <c r="B418" t="s">
-        <v>235</v>
+        <v>436</v>
       </c>
       <c r="C418">
         <v>693</v>
@@ -30772,7 +31563,7 @@
         <v>417</v>
       </c>
       <c r="B419" t="s">
-        <v>166</v>
+        <v>437</v>
       </c>
       <c r="C419">
         <v>847</v>
@@ -30843,7 +31634,7 @@
         <v>418</v>
       </c>
       <c r="B420" t="s">
-        <v>236</v>
+        <v>438</v>
       </c>
       <c r="C420">
         <v>897</v>
@@ -30914,7 +31705,7 @@
         <v>419</v>
       </c>
       <c r="B421" t="s">
-        <v>237</v>
+        <v>439</v>
       </c>
       <c r="C421">
         <v>773</v>
@@ -30985,7 +31776,7 @@
         <v>420</v>
       </c>
       <c r="B422" t="s">
-        <v>224</v>
+        <v>440</v>
       </c>
       <c r="C422">
         <v>671</v>
@@ -31056,7 +31847,7 @@
         <v>421</v>
       </c>
       <c r="B423" t="s">
-        <v>225</v>
+        <v>441</v>
       </c>
       <c r="C423">
         <v>706</v>
@@ -31127,7 +31918,7 @@
         <v>422</v>
       </c>
       <c r="B424" t="s">
-        <v>103</v>
+        <v>442</v>
       </c>
       <c r="C424">
         <v>1027</v>
@@ -31198,7 +31989,7 @@
         <v>423</v>
       </c>
       <c r="B425" t="s">
-        <v>238</v>
+        <v>443</v>
       </c>
       <c r="C425">
         <v>598</v>
@@ -31269,7 +32060,7 @@
         <v>424</v>
       </c>
       <c r="B426" t="s">
-        <v>103</v>
+        <v>444</v>
       </c>
       <c r="C426">
         <v>756</v>
@@ -31340,7 +32131,7 @@
         <v>425</v>
       </c>
       <c r="B427" t="s">
-        <v>239</v>
+        <v>445</v>
       </c>
       <c r="C427">
         <v>1120</v>
@@ -31411,7 +32202,7 @@
         <v>426</v>
       </c>
       <c r="B428" t="s">
-        <v>240</v>
+        <v>446</v>
       </c>
       <c r="C428">
         <v>1147</v>
@@ -31482,7 +32273,7 @@
         <v>427</v>
       </c>
       <c r="B429" t="s">
-        <v>52</v>
+        <v>447</v>
       </c>
       <c r="C429">
         <v>1153</v>
@@ -31553,7 +32344,7 @@
         <v>428</v>
       </c>
       <c r="B430" t="s">
-        <v>86</v>
+        <v>448</v>
       </c>
       <c r="C430">
         <v>1150</v>
@@ -31624,7 +32415,7 @@
         <v>429</v>
       </c>
       <c r="B431" t="s">
-        <v>60</v>
+        <v>449</v>
       </c>
       <c r="C431">
         <v>643</v>
@@ -31695,7 +32486,7 @@
         <v>430</v>
       </c>
       <c r="B432" t="s">
-        <v>61</v>
+        <v>450</v>
       </c>
       <c r="C432">
         <v>624</v>
@@ -31766,7 +32557,7 @@
         <v>431</v>
       </c>
       <c r="B433" t="s">
-        <v>79</v>
+        <v>451</v>
       </c>
       <c r="C433">
         <v>861</v>
@@ -31837,7 +32628,7 @@
         <v>432</v>
       </c>
       <c r="B434" t="s">
-        <v>84</v>
+        <v>452</v>
       </c>
       <c r="C434">
         <v>1122</v>
@@ -31908,7 +32699,7 @@
         <v>433</v>
       </c>
       <c r="B435" t="s">
-        <v>241</v>
+        <v>453</v>
       </c>
       <c r="C435">
         <v>453</v>
@@ -31979,7 +32770,7 @@
         <v>434</v>
       </c>
       <c r="B436" t="s">
-        <v>45</v>
+        <v>454</v>
       </c>
       <c r="C436">
         <v>712</v>
@@ -32050,7 +32841,7 @@
         <v>435</v>
       </c>
       <c r="B437" t="s">
-        <v>232</v>
+        <v>455</v>
       </c>
       <c r="C437">
         <v>755</v>
@@ -32121,7 +32912,7 @@
         <v>436</v>
       </c>
       <c r="B438" t="s">
-        <v>242</v>
+        <v>456</v>
       </c>
       <c r="C438">
         <v>990</v>
@@ -32192,7 +32983,7 @@
         <v>437</v>
       </c>
       <c r="B439" t="s">
-        <v>45</v>
+        <v>457</v>
       </c>
       <c r="C439">
         <v>820</v>
@@ -32263,7 +33054,7 @@
         <v>438</v>
       </c>
       <c r="B440" t="s">
-        <v>45</v>
+        <v>458</v>
       </c>
       <c r="C440">
         <v>753</v>
@@ -32334,7 +33125,7 @@
         <v>439</v>
       </c>
       <c r="B441" t="s">
-        <v>243</v>
+        <v>459</v>
       </c>
       <c r="C441">
         <v>838</v>
@@ -32405,7 +33196,7 @@
         <v>440</v>
       </c>
       <c r="B442" t="s">
-        <v>45</v>
+        <v>460</v>
       </c>
       <c r="C442">
         <v>730</v>
@@ -32476,7 +33267,7 @@
         <v>441</v>
       </c>
       <c r="B443" t="s">
-        <v>37</v>
+        <v>461</v>
       </c>
       <c r="C443">
         <v>839</v>
@@ -32547,7 +33338,7 @@
         <v>442</v>
       </c>
       <c r="B444" t="s">
-        <v>166</v>
+        <v>462</v>
       </c>
       <c r="C444">
         <v>961</v>
@@ -32618,7 +33409,7 @@
         <v>443</v>
       </c>
       <c r="B445" t="s">
-        <v>244</v>
+        <v>463</v>
       </c>
       <c r="C445">
         <v>367</v>
@@ -32689,7 +33480,7 @@
         <v>444</v>
       </c>
       <c r="B446" t="s">
-        <v>226</v>
+        <v>464</v>
       </c>
       <c r="C446">
         <v>618</v>
@@ -32760,7 +33551,7 @@
         <v>445</v>
       </c>
       <c r="B447" t="s">
-        <v>136</v>
+        <v>465</v>
       </c>
       <c r="C447">
         <v>1163</v>
@@ -32831,7 +33622,7 @@
         <v>446</v>
       </c>
       <c r="B448" t="s">
-        <v>137</v>
+        <v>466</v>
       </c>
       <c r="C448">
         <v>1017</v>
@@ -32902,7 +33693,7 @@
         <v>447</v>
       </c>
       <c r="B449" t="s">
-        <v>233</v>
+        <v>467</v>
       </c>
       <c r="C449">
         <v>819</v>
@@ -32973,7 +33764,7 @@
         <v>448</v>
       </c>
       <c r="B450" t="s">
-        <v>234</v>
+        <v>468</v>
       </c>
       <c r="C450">
         <v>483</v>
@@ -33044,7 +33835,7 @@
         <v>449</v>
       </c>
       <c r="B451" t="s">
-        <v>245</v>
+        <v>469</v>
       </c>
       <c r="C451">
         <v>1099</v>
@@ -33115,7 +33906,7 @@
         <v>450</v>
       </c>
       <c r="B452" t="s">
-        <v>226</v>
+        <v>470</v>
       </c>
       <c r="C452">
         <v>409</v>
@@ -33186,7 +33977,7 @@
         <v>451</v>
       </c>
       <c r="B453" t="s">
-        <v>226</v>
+        <v>471</v>
       </c>
       <c r="C453">
         <v>607</v>
@@ -33257,7 +34048,7 @@
         <v>452</v>
       </c>
       <c r="B454" t="s">
-        <v>9</v>
+        <v>472</v>
       </c>
       <c r="C454">
         <v>1093</v>
@@ -33328,7 +34119,7 @@
         <v>453</v>
       </c>
       <c r="B455" t="s">
-        <v>37</v>
+        <v>473</v>
       </c>
       <c r="C455">
         <v>802</v>
@@ -33399,7 +34190,7 @@
         <v>454</v>
       </c>
       <c r="B456" t="s">
-        <v>37</v>
+        <v>474</v>
       </c>
       <c r="C456">
         <v>942</v>
@@ -33470,7 +34261,7 @@
         <v>455</v>
       </c>
       <c r="B457" t="s">
-        <v>246</v>
+        <v>475</v>
       </c>
       <c r="C457">
         <v>646</v>
@@ -33541,7 +34332,7 @@
         <v>456</v>
       </c>
       <c r="B458" t="s">
-        <v>247</v>
+        <v>476</v>
       </c>
       <c r="C458">
         <v>656</v>
@@ -33612,7 +34403,7 @@
         <v>457</v>
       </c>
       <c r="B459" t="s">
-        <v>103</v>
+        <v>477</v>
       </c>
       <c r="C459">
         <v>934</v>
@@ -33683,7 +34474,7 @@
         <v>458</v>
       </c>
       <c r="B460" t="s">
-        <v>122</v>
+        <v>478</v>
       </c>
       <c r="C460">
         <v>662</v>
@@ -33754,7 +34545,7 @@
         <v>459</v>
       </c>
       <c r="B461" t="s">
-        <v>103</v>
+        <v>479</v>
       </c>
       <c r="C461">
         <v>405</v>
@@ -33825,7 +34616,7 @@
         <v>460</v>
       </c>
       <c r="B462" t="s">
-        <v>51</v>
+        <v>480</v>
       </c>
       <c r="C462">
         <v>968</v>
